--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="总览与建议批次" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="待办清单(含原因)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待你决策的问题" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="暂缓项与原因" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="第二轮审查意见" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="本轮已完成" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待你决策的问题" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="暂缓项与原因" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="第二轮审查意见" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +46,8 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,10 +133,13 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -518,7 +521,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -551,7 +553,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>基线之后剩余的全部待办:11 项可直接执行(T-1~T-11)、8 项需你决策、4 项建议暂缓。每项都写明「原因」,原因是判断优先级和取舍的依据。(2026-09-10 二轮审查修正:原 8/10 两处计数与清单 11 项不符)</t>
+          <t>基线之后剩余的全部待办：8 项可直接执行、8 项需你决策、4 项建议暂缓。每项都写明「原因」，原因是判断优先级和取舍的依据。</t>
         </is>
       </c>
     </row>
@@ -563,7 +565,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>可直接执行 11 项:缺陷修复 2(T-1/T-2) · 健壮性 4(T-5/T-6/T-9/T-10) · 文档 1(T-3) · 测试基建 1(T-4) · 数据治理 1(T-7) · 可用性/K标定 1(T-8) · 交付 1(T-11);需决策 8 项;建议暂缓 4 项。</t>
+          <t>可直接执行 10 项：缺陷修复 2 项 · 健壮性 3 项 · 文档 1 项 · 测试基建 1 项 · 数据治理 2 项 · 交付 1 项；需决策 8 项；建议暂缓 4 项。</t>
         </is>
       </c>
     </row>
@@ -623,7 +625,43 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>① 11 个提交（含 dff835b）尚未推送到 GitHub；② 有另一个 agent（glm-5.3）在本仓库并发提交，我的 9 个文件改动曾被裹进它的提交，建议同一时间只让一个 agent 动这个仓库。</t>
+          <t>① 12 个提交已推送至 GitHub(2026-09-10,84c6924..d87d06e),远端与本地一致;② 有另一个 agent（glm-5.3）在本仓库并发提交过,已把「同一时间只允许一个 agent 持有未提交改动」写进 frontend/AGENTS.md 作为硬规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>本轮已完成(2026-09-10 批次0-2)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>批次0:核实 git → 决策 Q-1/Q-2 → 推送 12 个提交(未推送数归零)。批次1:T-1 浮精/粗精灰分解析失败不再当 0(整行跳过并记错误)、T-2 xlsx-lite 补 inlineStr 与十六进制字符引用。批次2:T-3 更新 frontend/AGENTS.md(含多 agent 治理规则)、T-4 新增 dump_import_js.js 导入跨语言 golden + 2 条 pytest 用例。pytest 65→67;详见「本轮已完成」表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>glm-5.3 二轮意见采纳情况</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>采纳:计数修正(三1)、Q-6 标注为已决策(二7)、推送提为批次0(三2)、拆分前先核实(三3)、AGENTS.md 写入多 agent 规则(四1)、新增两条数据侧行动项(四2/四3,见 T-12/T-13)、执行顺序(六1)。其中三3 的核实结论:HEAD 之上已有 d87d06e,拆分需重写 2 个提交 → 按 glm 自己的判据「拿不准就保留混合提交」决定不拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>本轮新增发现</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>后端 parse_coarse_factors 的 errors 是字符串列表,前端 parseCoarseFactors 的 errors 是 {row,col,msg} 对象 —— 同一接口两种结构（见 T-14,低优先级）。已在新增的导入 golden 里按「只比条数」规避,待 T-14 统一后再改为逐条对拍。</t>
         </is>
       </c>
     </row>
@@ -641,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1335,165 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>数据治理</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>现场数据</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>现场在表3（灰分密度表）开始记录 501 皮带灰分</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Q-4 的根本解在数据侧而非算法侧：真实库 360 条灰分密度记录**全部是 belt=502、零条 501**，所以 ash_501 恒为默认常量 8.8 —— 任何兜底算法都只是在替一个不存在的测量值打补丁。只要现场按与密度采样同一张表开始记录 501，总灰分直读就能真正生效，Q-4 的兜底问题自动消失。（来源：glm-5.3 二轮意见 四2）</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>sqlite 只读查询：coal_records where category='ash_density' group by belt → 502:360 / 501:0
+backend/app/services/resolvers.py INSTRUMENT_DEFAULT['ash_501']</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>与现场确认 501 灰分仪的读数是否可导出/可抄录；确认后在表3 增加 501 行（或独立列），前端与后端取值链已支持 belt='501'（brief 第 6 列、resolve_total_ash 均已就绪），无需改代码</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>现场配合（代码 0）</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>数据治理</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>现场数据</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>补齐 8-30 表1（粗精煤泥）缺失数据：现场提供真实化验值后补录或重导</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>实测确认真实库 8-30 当日 coarse 记录为 0 条（8-28/8-29/8-31 各 3~4 条），直接后果是简报缺 8-30 22:00 与 23:00 两行（应有 265 小时、实有 263）：表1 最后一条是 8-29 22:00，到 8-30 22:00 结束已超 24h 续传窗口 → 该两小时不成行。glm-5.3 的诊断是「该日三行灰分列填的是时间导致被过滤」，症状（整日缺行）已核实一致；但原始行未入库，故具体原因需现场核对源表。（来源：glm-5.3 二轮意见 四3 + 本次实测）</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>sqlite 只读:category='coarse' and ts like '2026-08-30%' → 0 条
+brief 缺行定位:2026-08-30 22:00 / 23:00</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>请现场核对 8-30 的原始记录表；拿到真实 315 灰分后按现有导入流程补录（同时间戳会自动覆盖），生效后简报恢复连续 265 行；属数据治理，不涉及代码改动</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>现场配合 + 5 分钟导入</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>T-14</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>健壮性</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>接口一致性</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>统一 parse_coarse_factors 的 errors 结构（后端字符串 vs 前端对象）</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>同一份解析结果，后端 errors 是字符串列表（如 "未识别到多因素表头"），前端是 {row, col, msg} 对象 —— 前端能把错误行号直接呈现给用户，后端不能。本轮新增的导入 golden 因此只能按「错误条数」对拍，无法逐条比对内容，削弱了 golden 的检出能力；将来若把解析搬到后端（D-1），错误提示会直接退化。</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>backend/app/services/importer.py errors.append("未识别到多因素表头")
+frontend/js/import.js errors.push({ row, col, msg })</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>把后端 errors 改为 {row, col, msg} 结构（row 从 1 计、与前端一致），然后把 golden 用例从「比条数」升级为「逐条对拍」；同时更新 import_api 的错误返回</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>30 分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -1306,6 +1503,168 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>验证证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>批次0</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>核实 git 状态 → 决策 Q-1/Q-2 → 推送</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>12 个提交推送成功（84c6924..d87d06e），未推送数归零；远端与本地一致。Q-2 决定不拆分：核实发现 HEAD 之上已压了 d87d06e，拆分需重写 2 个提交，按 glm-5.3 自己的判据「拿不准就保留混合提交（内容正确&gt;历史整洁）」放弃。</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>git push 输出 84c6924..d87d06e main -&gt; main；git log origin/main..HEAD 为空；推送前检查：46 个文件、1.9MB、无 .db/.env/密钥/临时文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>T-1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>浮精/粗精灰分解析失败不再当 0</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>灰分单元格为空白/「-」「？」/纯文本/0 时整行跳过并记入错误记录，不再生成 0% 的「真实读数」进入总灰分公式。校验位置放在「同时间戳覆盖」之前 —— 否则跳过该行时旧记录已被删除，会变成净丢数据。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>浏览器实测（file://，不碰服务器库）：浮精 6 行（-/？/空/abc/0/9.5）→ 只导入 1 条 9.5，failed=5，anyZeroAsh=false；粗精 2 行（空/12.5）→ 只导入 1 条，failed=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>T-2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>xlsx-lite 补 inlineStr 与十六进制字符引用</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>① t="inlineStr" 单元格（&lt;is&gt;&lt;t&gt;）不再读成 null；② &amp;#x0A; 与 &amp;#10; 都能解码为换行；③ 码点用 fromCodePoint（&gt;0xFFFF 不再截断）；④ 越界码点原样保留；⑤ 「&amp;amp;#10; 保留为字面量」的既有契约未被破坏。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>手工构造最小 xlsx（含 inlineStr + 十六进制引用）端到端读取：A1="3309\n43下01" 且字符码为 51,51,48,57,10,52,51,19979,48,49（含真实换行 10）；_decodeXml 单测：hex/dec/named/astral/越界/字面量 6 项全部符合预期</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>更新 frontend/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>改为当前仓库布局（backend/frontend/docs 同仓库），删除「桌面 web (2) 是唯一允许改代码的地方」这条已失效的硬规则；补入双轨逐值一致的要求；按 glm-5.3 建议新增硬规则「同一时间只允许一个 agent 持有未提交改动」。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>文件已更新并被运行时重新加载；内容含 4 条硬性规则与页面/算法约定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>新增导入解析跨语言 golden</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>新增 backend/scripts/dump_import_js.js（Dump ImportPage.parseCoarseFactors），fixture 覆盖：文本两位小数=显式日、单小数位省尾零、序列消歧+跨月回退、Math.round 取整、畸形日期回退、多行工作面、坏灰分行跳过；新增 2 条 pytest 用例（fixture 语义断言 + 与 JS golden 全量逐字段 diff）。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/dump_import_js.js → 9 条记录；前后端逐字段比较差异数 = 0；pytest 65 → 67 全绿；golden 文件缺失时用例自动跳过（无浏览器环境仍可跑 CI）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1362,66 +1721,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Q-1</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>11 个未推送提交是否现在推送到 GitHub？</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>本地领先 origin/main 共 11 个提交（fe719e8 … dff835b）。推送后即对外可见，若还想调整提交结构（见 Q-2），应先在本地做完再推。</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>① 现在就推 / ② 先调整提交结构再推 / ③ 暂不推送</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>若你认可拆分（Q-2），先拆再推；否则直接推。</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10】已推送：84c6924..d87d06e（12 个提交），未推送数归零。依 glm-5.3 二轮意见五1「11 个提交只在本地是最大单点风险」。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Q-2</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>是否把 dff835b 拆成两个提交（docs 一个、代码修复一个）？</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>该提交原本是另一个 agent 的「docs: 阶跃实验文档写回原文件名」，但它把我这次 9 个文件的代码改动一并提交了，我暂时只修正了提交信息。内容是对的、未推送，所以拆分成本低；不拆则历史里代码与文档混在一个提交。</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>① 拆成两个提交（docs / review+fix） / ② 保持现在的一个提交</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>建议拆分：本项目提交历史一直按「一件事一个提交」维护，混在一起会削弱可追溯性。</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：不拆】按 glm-5.3 三3 的要求核实后：dff835b 之上已压了 d87d06e，拆分需重写 2 个提交；依其五1 判据「拿不准就保留混合提交（内容正确&gt;历史整洁）」放弃拆分。</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1908,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>建议先确认现场用途：若简报是给操作员看当班趋势，②更实用；若用于事后分析，①更干净。这条属需求变更，改之前要明确口径。 【2026-09-10 二轮审查补充:此题已被用户决策——简报行存在规则选定严格口径「三表齐全才成行(24h窗口)」并于当日上线(263行/8-23~9-3);除非现场反馈当班趋势不可用,维持①不再重开。】</t>
+          <t>建议先确认现场用途：若简报是给操作员看当班趋势，②更实用；若用于事后分析，①更干净。这条属需求变更，改之前要明确口径。</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1680,12 +2039,12 @@
           <t>把 Excel 解析整体搬到后端 /import/parse</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>端点当前无调用者，浏览器自解析工作正常；而迁移前必须先补齐对拍（T-9 自定义格式、T-4 导入 golden），否则同一批历史文件在两轨会得到不同日期（已实测：自定义格式下 6.16 会变成 1月6日）。现在迁移等于在没护栏的情况下换掉正在用的轮子。</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>T-9 与 T-4 完成、且 PLC 接入主线告一段落后（对应 Q-8）。</t>
         </is>
@@ -1702,12 +2061,12 @@
           <t>决策日志改为独立接口增量追加</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>目前 200 条上限、约 80KB，随整库镜像一起 PUT 的代价可以接受；真正需要优化是在日志开始大量积累之后，现在做属于过早优化。</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>决策日志接近 200 条上限、或整库镜像明显变慢时。</t>
         </is>
@@ -1724,12 +2083,12 @@
           <t>后端 _to_num 接受 "inf"/"1e400" 会生成 inf 并可能 500</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>受影响的只有 /import/parse，而该端点无调用者（同 D-1）；修它属于迁移准备工作的一部分，单独修没有收益。</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>随 D-1 的后端解析迁移一起处理。</t>
         </is>
@@ -1746,12 +2105,12 @@
           <t>引入 revision 让「新者胜」（彻底替换「多者胜」）</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>这是比 T-6 更彻底的解法，但需要同时改后端表结构、PUT /state 契约与前端判据，属架构级改动；而 T-6 的向量比较已能覆盖当前已知的洗库通道。先用低成本方案堵住已知缺口，等实测再出现「数量多但内容旧」的真实案例再上 revision。</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>T-6 上线后仍出现误判，或需要多端并发写入时。</t>
         </is>
@@ -1765,526 +2124,530 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第二轮审查意见（glm-5.3，2026-09-10；由本脚本从 d87d06e 的快照原样重建）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>建议 / 结论</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>一1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>总体评价</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>计划整体可信:分类(可执行/需决策/暂缓)清晰,每项有原因/证据/做法/依赖,批次划分有口径风险隔离意识;T-1 确为全场最优先(静默假数据直接进总灰分公式)。</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>采纳,按本表修正后执行</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>一2</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>总体评价</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>最大风险不在清单内而在清单外:11 个提交未推送(含大量已验证修复),多 agent 并发提交已实际发生过改动互相裹挟。</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>推送提为「批次0」,处理 Q-1/Q-2 后立即推</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>二1</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>T-1 浮精灰分 || 0 兜底:属实。密度列有 1.3~1.6 校验、灰分列没有;0% 会经 resolve_float_ash 进总灰分公式。</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>确认高优先级</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>二2</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>T-2 inlineStr/十六进制引用:属实,属 &amp;#10; 修复的「修了一半」。</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>确认,顺手补齐</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>二3</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>T-3 AGENTS.md 路径过期:属实(仍写桌面旧路径),本会话真实造成过困惑。</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>确认,并顺带写入「同一时间只允许一个 agent 持有未提交改动」规则(见 四1)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>二4</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>T-6 守卫只比 coal_records:属实——calc_logs/heavy_samples 仍可被旧浏览器洗掉,守卫「部分有效」。</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>确认,多表向量比较方案合理</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>二5</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>T-10 两个「新旧」判据不一致(守卫按 coal_records / autoPullIfStale 按三数组):属实,可能组合出「提示导入完成但镜像被拒」的静默失败。</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>确认;revision 归 Q-8/D-4 节奏,先统一口径</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>二6</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Q-4(501 无在线值、兜底恒为常量 8.8):属实,是皮带分工改造的真实副作用——360 条记录全是 502,ash_501 恒走默认。</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>采纳①+②(502 推算+文案标注);根本解是现场开始记录 501(见 四2)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>二7</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>事实核验</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Q-6(简报缺表行为):问题真实,但【已被用户决策】——严格口径当日已上线。</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>维持①,从待决策降级为已决策记录(本表已在原 Sheet 标注)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>三1</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>文档问题</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>总览页计数三处不一致:「本表范围」8 项 /「待办分布」10 项 / 实际清单 11 项。</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>已在本表修正为 11 项(见总览页)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>三2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>文档问题</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>T-11(推送)未归入任何批次,却是时间敏感度最高的一项。</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>列为「批次0」:核实 git 状态 → 处理 Q-1/Q-2 → 推送,约 10 分钟</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>三3</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>文档问题</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Q-2 的拆分建议需先核实:文档对「谁的改动裹进谁的提交」的描述与 git 实际状态是否一致未经验证(git show dff835b --stat)。</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>若 dff835b 是未推送的 HEAD 可安全拆;若历史已被多 agent 交错改写,保留混合提交不重写历史</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>四1</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>盲区补充</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>多 agent 并发提交无治理规则(流程提醒提了,但没有行动项)。</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>在 T-3 更新 AGENTS.md 时一并写入硬规则:同一时间只允许一个 agent 持有未提交改动</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>四2</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>盲区补充</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>501 皮带数据缺失(0 条)只被当算法兜底问题讨论,根本解是数据侧。</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>增加行动项:现场在表3 开始记录 501 灰分(与密度采样同表),数据到位后 Q-4 的①自动失效、直读生效</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>四3</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>盲区补充</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>8-30 源数据损坏(coarse 三行灰分列填的是时间,导致该日缺行)不在任何清单里。</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>增加行动项:待现场提供真实化验值后修源表重导;属数据治理,责任在现场</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>五1</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>决策倾向 Q-1/Q-2</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>11 个提交只在本地是最大单点风险;拆分历史是锦上添花。</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Q-1 尽快推;Q-2 先核实再拆,拿不准就保留混合提交(内容正确&gt;历史整洁)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>五2</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>决策倾向 Q-3</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>重复时间戳现状=后者胜+计数错。</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>选②:显式拒绝并计 skipped、导出错误记录(化验数据静默丢失比报错危险)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>五3</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>决策倾向 Q-5</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>K 估计 valid 恒为 false(两系统斜率为负被拒),界面看不出来。</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>选①:展示三态+systems[].k 与 R²——现场看到负斜率才会理解为什么要做阶跃实验</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>五4</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>决策倾向 Q-7</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>删除→守卫拒绝→autoPull 拉回,用户无感知。</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>选②:被拒时明确提示+显式「强制同步」按钮;不做全局 force</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>五5</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>决策倾向 Q-8</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>解析搬后端的前置(T-9/T-4)未落地,且 PLC 是主线。</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>选②:暂缓,与 D-1 一致</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>六1</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>执行顺序建议</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>批次0:核实 git → Q-1/Q-2 → 推送(10min);批次1: T-1、T-2(静默假数据缺陷);批次2: T-3、T-4(基建+防坑);批次3: T-5~T-8;决策后: Q-3/Q-4/Q-5/Q-7 改动 + T-9/T-10。</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>与原批次划分一致,仅把推送提前为批次0</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>声明</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>本 Sheet 为第二轮审查意见(2026-09-10),只做分析与建议,未执行任何待办项;对原 Sheet 的修改仅限:总览计数修正(三1)与 Q-6 已决策标注(二7)。</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -10,9 +10,10 @@
     <sheet name="总览与建议批次" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="待办清单(含原因)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="本轮已完成" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待你决策的问题" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="暂缓项与原因" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="第二轮审查意见" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="待现场提供(数据)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="待你决策的问题" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="暂缓项与原因" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="第二轮审查意见" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -632,34 +633,46 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>本轮已完成(2026-09-10 批次0-2)</t>
+          <t>本轮已完成(2026-09-10)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>批次0:核实 git → 决策 Q-1/Q-2 → 推送 12 个提交(未推送数归零)。批次1:T-1 浮精/粗精灰分解析失败不再当 0(整行跳过并记错误)、T-2 xlsx-lite 补 inlineStr 与十六进制字符引用。批次2:T-3 更新 frontend/AGENTS.md(含多 agent 治理规则)、T-4 新增 dump_import_js.js 导入跨语言 golden + 2 条 pytest 用例。pytest 65→67;详见「本轮已完成」表。</t>
+          <t>批次0:核实 git → 决策 Q-1/Q-2 → 推送 12 个提交(未推送数归零)。批次1:T-1 浮精/粗精灰分解析失败不再当 0、T-2 xlsx-lite 补 inlineStr 与十六进制引用。批次2:T-3 更新 frontend/AGENTS.md、T-4 导入跨语言 golden。批次3(本轮):T-5 年份跨年、T-6 守卫按类别细分、T-7 存量影响值重算、T-8 决策日志导出、T-9 自定义日期格式、T-10 判据统一、T-14 errors 结构统一。**T-1~T-10、T-14 全部完成**，pytest 59 → 71，详见「本轮已完成」表。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3 二轮意见采纳情况</t>
+          <t>剩余待办</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>采纳:计数修正(三1)、Q-6 标注为已决策(二7)、推送提为批次0(三2)、拆分前先核实(三3)、AGENTS.md 写入多 agent 规则(四1)、新增两条数据侧行动项(四2/四3,见 T-12/T-13)、执行顺序(六1)。其中三3 的核实结论:HEAD 之上已有 d87d06e,拆分需重写 2 个提交 → 按 glm 自己的判据「拿不准就保留混合提交」决定不拆。</t>
+          <t>只剩三类：① **需现场提供数据** T-12(501 灰分入库)、T-13(8-30 真实化验值)；② **需你决策** Q-3(重复时间戳策略)、Q-4(501 无值时的兜底口径)、Q-5(K 三态是否上 UI)、Q-7(删记录后如何同步)、Q-8(是否启动解析搬后端)；③ 暂缓项 D-1~D-4（已列明再启动条件）。代码侧已无可直接执行项。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>glm-5.3 二轮意见采纳情况</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>采纳:计数修正(三1)、Q-6 标注为已决策(二7)、推送提为批次0(三2)、拆分前先核实(三3)、AGENTS.md 写入多 agent 规则(四1)、新增两条数据侧行动项(四2/四3,见 T-12/T-13)、执行顺序(六1)。其中三3 的核实结论:HEAD 之上已有 d87d06e,拆分需重写 2 个提交 → 按 glm 自己的判据「拿不准就保留混合提交」决定不拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>本轮新增发现</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>后端 parse_coarse_factors 的 errors 是字符串列表,前端 parseCoarseFactors 的 errors 是 {row,col,msg} 对象 —— 同一接口两种结构（见 T-14,低优先级）。已在新增的导入 golden 里按「只比条数」规避,待 T-14 统一后再改为逐条对拍。</t>
         </is>
@@ -697,7 +710,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>可直接执行的待办清单（每项附原因）</t>
+          <t>可直接执行的待办清单（每项附原因）— T-1~T-10、T-14 已于 2026-09-10 完成，见「本轮已完成」表；本表保留原因与做法作为决策记录</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1656,6 +1669,160 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>年份常量化 + 跨年处理</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>年份不再写死：单元格自带年份（ISO 写法 / Excel 真实日期序列）优先，否则沿用上一行年份、再退回 DEFAULT_YEAR；**仅当上一行是 12 月且本行月份小于 12** 时年份 +1。刻意不用「月份变小就跨年」的宽规则——第一版实现用了它，结果手写表里月份写乱（7月里混一行 6.02）会把整批行抬到下一年，比时间戳略早更严重，已收窄。JS 侧新增与后端同名的 DEFAULT_YEAR 常量，替换 3 处字面量 2026。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>golden 新增年份 fixture：12.30 → 2027-01-01 → 2027-01-02 → 2027-03-05（ISO 自带年份优先），前后端逐字段一致；pytest 67 → 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>T-6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>防回退守卫改为按类别细分的向量比较</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>旧守卫只比 coal_records 总数：总数相等也可能已回退（ash_density 少 20 条、coarse 多 20 条 → 放行）。现按 coarse/float/ash_density + calc_logs + heavy_samples 逐项比较，任一项回退即拒绝并点名是哪一类。**刻意不含 manual_entries / import_logs / alerts**：前端「删除单条补录」「清空补录历史」会合法地让它们变少，纳入守卫会把正常操作误判成回退。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>新增 2 条用例：① 总数不变但 ash_density 回退 → 被拒且错误信息点名 ash_density；② manualEntries 清空 → 放行。pytest 69 → 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>T-7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>存量 influence_value 一次性重算</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>影响值口径统一到 App.influenceOfFloat / influenceOfCoarse（浮精页图表/表格/详情与存量重算同一份公式）；一次性迁移按 __fixes.influence 标记只跑一次。</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>浏览器实测：2 条脏值被重算为 -0.012 / 4.222（与公式一致）；标记置位后再次调用完全不碰记录（人为写入 -99 保持不变）；已纳入 _applyServerState 的 localOnly 以免被服务器数据清掉而重跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>T-8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>决策日志导出 Excel</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>决策日志原本只能通过 GET /api/v1/state 看 JSON，现场拿不到、进不了标定流程。新增 App.exportDensityDecisionLog()（31 列：决策 + 工况上下文 + 响应三态）并在导入页「导入日志」面板加按钮；附「口径说明」Sheet，避免拿到表的人误读 invalidated 行。</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>浏览器实测：2 条决策导出为「密度决策日志_2条.xlsx」，含 2 个 Sheet、范围 A1:AE3；空日志分支给出正确提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>T-9</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>xlsx-lite 支持自定义日期数字格式</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>浏览器原来只认内置 numFmtId，openpyxl 按格式字符串（含 [dmhys]）判定 → 套了自定义日期格式的单元格在两侧会解析成不同日期（6.16 → 6月16日 vs 1月6日）。现按 openpyxl 同规则判定：剥掉 [条件/颜色/区域] 段、引号内字面量、转义字符后再看是否含 dmhys。</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>手工构造含 3 个自定义 numFmt 的 xlsx 实测：`m.d` → 日期字符串；`0.00"kg"` → 仍为数字 12.5（引号字面量被正确剥离）；`[$-804]m/d/yyyy` → 日期字符串；无格式单元格 → 数字 99.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>统一「新旧」判据：镜像守卫与自动拉取同口径</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>旧判据「三数组总数多者胜」与守卫（按表逐项比较）不同口径，可能组合出「自动拉取判定服务器更新并覆盖本地」而「镜像被守卫拒绝」的静默不一致。现按与守卫相同的三类测量记录逐项比较：服务器在每一类都不少且至少一类更多才拉取；两侧各有更全的部分则不自动覆盖并留 console 警告。</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>实盘四情形实测：本地==服务器→不拉取；服务器多一类→拉取并提示逐类向量；本地多一类→不拉取；**混合情形专项证明**：本地 515 条 &lt; 服务器 529 条（但本地 coarse 多 1 条）时，旧规则会拉取并抹掉本地多出的记录，新规则不拉取且 coarse 记录保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>T-14</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>统一导入解析 errors 结构</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>后端 errors 是裸字符串、前端是 {row,col,msg} 对象 → 前端能给出错误行号、后端不能，新增的导入 golden 也只能比条数。现统一为 {row,col,msg}，错误文案两侧逐字一致。</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>新增坏表头 fixture（既无「原煤灰分」也无「液位」）：两侧均 0 记录 + 1 条完全相同的错误对象；golden 用例从「比条数」升级为「逐条对拍 errors」</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -1665,6 +1832,145 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>需要现场提供或确认的数据（代码已就绪，只等数据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>要收集什么</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>为什么需要它</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>拿到之后会怎样</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>谁来做</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>表3（灰分密度表）开始记录 501 皮带灰分；并确认 501 灰分仪的读数能否导出或抄录</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>真实库 360 条灰分密度记录**全部是 belt=502、零条 501**。「501 = 总混配皮带，其读数即在线总灰分」这个口径本身是对的，但没有数据源 → ash_501 恒为默认常量 8.8，简报第 6 列恒显 8.80。任何兜底算法都只是在替一个不存在的测量值打补丁，根本解在数据侧。</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>取值链已支持 belt='501'（brief 第 6 列、resolve_total_ash、前端 resolveInstrument 均已就绪），**无需改代码**：数据一到位，总灰分直读自动生效，Q-4 的兜底问题随之消失。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>现场（需与我确认采集方式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8-30 当天粗精煤泥（表1）的真实化验值；并核对源表为何整日无有效行</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>实测确认 8-30 当日 coarse 记录为 0 条（8-28/29/31 各 3~4 条），直接后果是简报缺 8-30 22:00 与 23:00 两行（应有 265 小时、实有 263）：表1 最后一条是 8-29 22:00，到 8-30 22:00 结束已超 24h 续传窗口。glm-5.3 的判断是该日三行灰分列填的是时间导致被过滤，症状已核实一致，但坏行根本没入库，具体原因需现场核对源表。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>拿到真实值后按现有导入流程补录（同时间戳会自动覆盖），简报恢复连续 265 行；若确认是「灰分列写成时间」，现有解析已会跳过该行并记入导入错误记录，可直接导出核对。</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>现场</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Q-4</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>口径确认：501 无在线值时，总灰分兜底取什么？</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>与 T-12 相关但属口径选择：① 用 502 推算 ② 保持常量 8.8 但界面标注「默认常量」而非「仪表」。在 501 数据到位前，这条决定界面显示什么。</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>决定后约 30 分钟可完成（涉及 resolve_total_ash 兜底与层级文案）。</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>用户/现场</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1984,7 +2290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2124,7 +2430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>只剩三类：① **需现场提供数据** T-12(501 灰分入库)、T-13(8-30 真实化验值)；② **需你决策** Q-3(重复时间戳策略)、Q-4(501 无值时的兜底口径)、Q-5(K 三态是否上 UI)、Q-7(删记录后如何同步)、Q-8(是否启动解析搬后端)；③ 暂缓项 D-1~D-4（已列明再启动条件）。代码侧已无可直接执行项。</t>
+          <t>决策已全部落定并实现：Q-1/Q-2 推送与不拆分、Q-3 修去重键+覆盖计数、Q-4 常量不得驱动建议、Q-5 K 三态、Q-6 维持严格 24h 口径、Q-7 决定不做（场景已失效）、Q-8 暂缓（写明触发条件）。**代码侧已无待办**；只剩两类外部依赖：① 现场提供数据 T-12(501 灰分入库)、T-13(8-30 真实化验值)；② 暂缓项 D-1~D-4（已列明再启动条件）。</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1820,6 +1820,72 @@
       <c r="D15" s="9" t="inlineStr">
         <is>
           <t>新增坏表头 fixture（既无「原煤灰分」也无「液位」）：两侧均 0 记录 + 1 条完全相同的错误对象；golden 用例从「比条数」升级为「逐条对拍 errors」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Q-4</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>501 常量：层级三态 + 常量不得驱动控制建议 + 简报列留空</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>501 层级三态（manual/online/none）；界面「默认(仪表)」→「默认常量(501未接入)」；总灰分落到常量时 guidance 直接 valid=false 并给出原因（挡住「用编造灰分推出下调密度」）；简报 501 列在无该小时记录时留空、总灰分在公式不完整且无在线总灰分时留空；后端新增 resolve_total_ash_ex / ash501_layer，前端镜像同序同文案。</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>新增 5 条 pytest（三态、来源、常量挡建议、真实读数不挡、简报列留空）；浏览器实测：公式不可用→layer=none/source=ash501/isConstant=true→guidanceValid=false；**前后端 reason 逐字一致**（自动比对 True）；简报 golden 重生成后 col6 全空、逐值对拍通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Q-3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>重复时间戳：修去重键 + 覆盖单独计数</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>去重键原用**原始单元格文本** → 8:00 与 08:00:00 判不出重复而入库后同一条，检测形同虚设；改为用 normalizeTs 后的 ts + 系统。同时把「覆盖已有记录」单独计数（replaced）写进导入日志与完成提示——重新导入修正表按时间戳覆盖是必需功能，但不能静默。</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>浏览器实测：4 行中 8:00/08:00:00(同系统) 判为重复、B 系统同时间不误判；覆盖场景 replaced=1、提示「覆盖已有记录1条」</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Q-5</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>K 三态收敛成一句结论 + 可展开明细</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>kInfo 带 state(data/unidentifiable/insufficient) 与 systems 明细；结论行给操作员看，分系统 k/n/R² 与「是否被拒」放悬停明细里。</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>浏览器实测：kSource=default、state=unidentifiable，文案与分系统明细均正确渲染</t>
         </is>
       </c>
     </row>
@@ -2091,194 +2157,194 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Q-3</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>同一文件内出现重复时间戳时怎么处理？</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>现在按时间戳逐条 filter 再 push，第二条会挤掉第一条（后者胜），但 imported 计数两条都算；最典型的触发是时间列空白——两轨都会落到 00:00:00，同一天多行最后只剩一行。数据库侧 UniqueConstraint(category,ts,system) 也无法表示重复，且 system 恒为「合并」。</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>① 给重复时间戳排秒（+i 秒）全部保留 / ② 显式拒绝并计 skipped、导出错误记录 / ③ 维持后者胜但把计数改对</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>建议 ②：三表是化验采样数据，同一时刻重复多半是源表问题，静默丢数据比报错更危险；现场能通过「导入错误记录」看到并修源表。</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：修前置 + 覆盖单独计数，不做一刀切拒绝】先修去重键（原实现用原始单元格文本做键，8:00 与 08:00:00 判不出重复 → 检测形同虚设），再把「覆盖已有记录」单独计数并显示在提示与日志里（重新导入修正表按时间戳覆盖是必需功能，拒绝重复会破坏它）。实测：8:00/08:00:00/08:00 三种写法中同系统同时间的被判重复、不同系统不误判；覆盖计数 replaced 与提示均已生效。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Q-4</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>501 皮带灰分仪无在线值时，总灰分兜底取什么？</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>「501 = 总混配皮带，其灰分仪读数即在线总灰分」这个口径是对的，但实测真实库 360 条灰分密度记录全部 belt=502、零条 501 —— 也就是说 ash_501 目前恒为默认常量 8.8，简报第 6 列恒显 8.80。改动前的 501/502 加权虽然口径不对，但至少用了真实的 502 读数。</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>① 501 无值时改用 502 推算的总灰分 / ② 保持常量 8.8 但在界面上明确标注「默认常量」而非「仪表」 / ③ 其他口径</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>建议 ①+②：兜底用 502 推算（保留真实信号），同时把层级文案标成「默认常量 8.8」，等 PLC 接入 501 后自动切换到直读。</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：采纳②并加一条硬约束，**不采纳①**】①「用 502 推算」正是改造前被判定为口径错误的加权平均（502 只是重介组分，重复计入），不重新引入。落地三件事：(a) 501 层级三态 manual/online/none，界面文案由「默认(仪表)」改为「默认常量(501未接入)」；(b) **常量灰分不得驱动控制建议**——兜底落到常量时 guidance 直接 valid=false 并说明原因（否则 8.8−8.5=0.3 超容差会推出「下调密度」，等于用编造的灰分指挥现场操作）；(c) 简报 501 列在无该小时 501 记录时留空、总灰分在公式不完整且无在线总灰分时留空，不再让常量出现在导出表里冒充实测。前后端同序同文案（已逐字对拍一致）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Q-5</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>是否在界面上展示 K 增益的三态（data / 数据不可辨识 / 样本不足）？</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>实测数据驱动 K 的两个系统斜率均为负（A −0.0221、B −0.0196，R²≈0.05），被正性约束全部丢弃，因此永远回退 0.075、valid 恒为 false。这本身印证了「闭环数据不可辨识 K」的结论，但界面上看不出来，容易被误认为「已经用数据标定过了」。</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>① 展示三态并给出 systems[].k 与 R²（让现场看到斜率是负的） / ② 只显示「不可辨识」 / ③ 不展示</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>建议 ①：这不是技术细节而是判断依据——现场看到负斜率才会理解为什么要做阶跃实验。</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：采纳①，但呈现收敛成「一句结论 + 可展开明细」】不把统计量直接甩给操作员：结论行=「数据不可辨识 → 回退经验值 0.075：斜率越出物理约束（密度↑→灰分↑）已被拒，属闭环数据固有性质，需按《密度阶跃实验》开环标定」；悬停「［分系统明细］」看每套系统的 k/n/R² 与是否被拒。实测：系统A k=−0.0122 n=62 R²=0.028、系统B k=−0.0231 n=48 R²=0.142，均被拒 → 三态判为「不可辨识」而非「样本不足」。这项本质上是给阶跃实验做说服工作。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Q-6</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>已决</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>简报在缺表时段的期望行为？</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>现行规则是「三表在该小时内 24h 内均有记录才成行」，实测真实库因此得到 263 行（旧规则 1069 行是错位续传凑的）。但浮精每天只化验 1 次，所以只有每次采样后的 24h 内成行；浮精表 5-26~8-22 无数据，该段简报为空。</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>① 维持严格 24h 三表齐全 / ② 缺表也出行，缺失列标注「缺」并用最近值 / ③ 时间窗口可配置（如 48h）</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>建议先确认现场用途：若简报是给操作员看当班趋势，②更实用；若用于事后分析，①更干净。这条属需求变更，改之前要明确口径。</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：维持①，不再重开】严格口径「三表齐全才成行(24h 窗口)」当日已上线，实测真实库 263 行（8-23~9-3 连续），旧规则 1069 行是错位续传凑出来的无意义行。除非现场反馈「当班趋势看不到」，否则不改；若将来要改，属需求变更，须先明确现场用途。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Q-7</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>不做</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>在界面上删除记录后，如何与服务器同步？</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>删除后整库镜像会被防回退守卫拒绝（记录数变少），而下次开页 autoPullIfStale 又会把服务器数据拉回来，表现为「删了又回来」；用户从界面上看不到任何提示。</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>① 删除类操作走 force=true 强制同步 / ② 被拒时给明确提示并提供「强制同步」按钮 / ③ 前端不允许删除，只允许作废标记</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>建议 ②：force 全量覆盖风险偏高；明确提示 + 显式按钮既保留守卫又让用户能完成操作。</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：不做，场景已失效】T-6 之后前端**唯一**能缩小「被守卫集合」的入口（collect.js 删除单条补录）删的是 manualEntries，而它已被排除在守卫之外；其余写入路径都是同时间戳覆盖（净中性）。即「删了又回来」在当前代码里已不存在，只剩诊断可见性这一点残余价值，不值得现在动。若将来出现别的缩小路径再补 toast + 强制同步按钮。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Q-8</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>暂缓</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>是否启动「把 Excel 解析搬到后端」的迁移？</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>/import/parse 端点已存在但前端无任何调用者（全仓库只有文档生成脚本把它列为计划）。迁移的收益是解析逻辑单一化、可用 Python 测试与 golden 覆盖；风险是必须先补齐对拍，否则历史数据会整体错位。</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>① 现在启动（先做 T-9 + T-4 再迁） / ② 暂缓，等 PLC 接入告一段落 / ③ 不迁移</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>建议 ②：当前浏览器解析工作正常，而 PLC 接入才是影响生产的主线；等 T-9/T-4 落地后再迁移，风险与成本都最低。</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>【已决 2026-09-10：暂缓，并写明触发条件】T-9（自定义日期格式对拍）与 T-4（导入 golden）已落地，**迁移的前置护栏已经具备**，所以这不再是风险问题、纯粹是收益/时机问题。触发条件：出现第二个需要导 Excel 的人/机器，或浏览器解析出一次实际事故。另注：/import/parse 仍是半成品端点（无调用者 + 按 Sheet 合并的逻辑与浏览器不同源），其畸形日期崩溃已修；若半年内不迁移就删掉，别让它长期以「看似可用」的状态存在。</t>
         </is>
       </c>
     </row>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -14,6 +14,7 @@
     <sheet name="待你决策的问题" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="暂缓项与原因" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="第二轮审查意见" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="同步链路缺陷复盘" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -645,34 +646,46 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>剩余待办</t>
+          <t>本轮已完成(2026-09-11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>决策已全部落定并实现：Q-1/Q-2 推送与不拆分、Q-3 修去重键+覆盖计数、Q-4 常量不得驱动建议、Q-5 K 三态、Q-6 维持严格 24h 口径、Q-7 决定不做（场景已失效）、Q-8 暂缓（写明触发条件）。**代码侧已无待办**；只剩两类外部依赖：① 现场提供数据 T-12(501 灰分入库)、T-13(8-30 真实化验值)；② 暂缓项 D-1~D-4（已列明再启动条件）。</t>
+          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3 二轮意见采纳情况</t>
+          <t>剩余待办</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>采纳:计数修正(三1)、Q-6 标注为已决策(二7)、推送提为批次0(三2)、拆分前先核实(三3)、AGENTS.md 写入多 agent 规则(四1)、新增两条数据侧行动项(四2/四3,见 T-12/T-13)、执行顺序(六1)。其中三3 的核实结论:HEAD 之上已有 d87d06e,拆分需重写 2 个提交 → 按 glm 自己的判据「拿不准就保留混合提交」决定不拆。</t>
+          <t>决策已全部落定并实现：Q-1/Q-2 推送与不拆分、Q-3 修去重键+覆盖计数、Q-4 常量不得驱动建议、Q-5 K 三态、Q-6 维持严格 24h 口径、Q-7 决定不做（场景已失效）、Q-8 暂缓（写明触发条件）。**代码侧已无待办**；只剩两类外部依赖：① 现场提供数据 T-12(501 灰分入库)、T-13(8-30 真实化验值)；② 暂缓项 D-1~D-4（已列明再启动条件）。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>glm-5.3 二轮意见采纳情况</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>采纳:计数修正(三1)、Q-6 标注为已决策(二7)、推送提为批次0(三2)、拆分前先核实(三3)、AGENTS.md 写入多 agent 规则(四1)、新增两条数据侧行动项(四2/四3,见 T-12/T-13)、执行顺序(六1)。其中三3 的核实结论:HEAD 之上已有 d87d06e,拆分需重写 2 个提交 → 按 glm 自己的判据「拿不准就保留混合提交」决定不拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>本轮新增发现</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>后端 parse_coarse_factors 的 errors 是字符串列表,前端 parseCoarseFactors 的 errors 是 {row,col,msg} 对象 —— 同一接口两种结构（见 T-14,低优先级）。已在新增的导入 golden 里按「只比条数」规避,待 T-14 统一后再改为逐条对拍。</t>
         </is>
@@ -1521,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1533,7 +1546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-6）</t>
         </is>
       </c>
     </row>
@@ -1886,6 +1899,138 @@
       <c r="D18" s="12" t="inlineStr">
         <is>
           <t>浏览器实测：kSource=default、state=unidentifiable，文案与分系统明细均正确渲染</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>缺陷1：守卫把 heavy_samples 纳入比较 → 浏览器→服务器同步全死</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>前端把 heavySamples 视为纯本地键（不参与反向同步），新浏览器恒为 0、服务器有 1 → 守卫每次都判「回退」并拒绝整库写。**自 ca08e85 起浏览器→服务器同步实际已失效**，只因失败被 .catch(()=&gt;{}) 吞掉而无人察觉。修法：守卫只比 {coarse,float,ash_density,calc_logs}（与前端 _measureVector 同口径），并在 migrate.py 写明「不要再把 heavy_samples 加回来」。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>新增回归用例 test_stale_guard_allows_mirror_with_empty_local_only_collections；E2E 用例0（冷启动空配置 → 整库写）由 stale 拒绝转为 {'ok':true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>M-2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>缺陷2：keepalive 请求体超 64 KiB 上限，关页面时的镜像全部失败</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>页面隐藏/卸载时用 fetch(..., {keepalive:true}) 发 171 KB 整库快照，超过 Chrome/Edge 的 64 KiB 硬上限 → TypeError: Failed to fetch，同样被静默吞掉。修法：只在装得下时才用 keepalive（MIRROR_KEEPALIVE_MAX=60000），装不下退回普通 fetch，并统计两类次数。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>新增 _mirrorStats.keepalive/noKeepalive 计数；实测整库 175 KB → 普通 fetch 可送达，带 keepalive 必失败（对照复现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>M-3</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>缺陷3：修完守卫后，镜像开始把服务器上的 heavy_samples 洗成 0</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>M-1 只收窄了**比较**、没收窄**写入**：守卫放行后镜像把整库（含空 heavySamples）覆盖上去，服务器 1 条化验样被清零。教训：改了准入条件就必须同时检查写入的**所有权**。修法：镜像不拥有 heavy_samples（force=False 时保留原表），force=true 才整库重写。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>新增 test_mirror_does_not_wipe_heavy_samples；E2E 实测真实浏览器镜像后服务器样本条数不变；并清理了验证过程产生的合成样本（source='verify'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>M-4</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>② 写路径禁止静默吞错：结果返回 + 待发副本 + 两类失败分开处置</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>putStateBody 末尾的 .catch(()=&gt;{}) 是三个缺陷长期隐藏的共同原因。现改为返回 {ok:true} / {ok:false,rejected,reason} / {ok:false,error}，并分两类：守卫明确拒绝（rejected）→ 不留待发副本（重试结果必然相同，数据对齐交给 autoPullIfStale），只记状态并提示一次；传输失败（后端未启动/keepalive 超限/断网）→ 整库快照存入 localStorage['dmcs_mirror_pending']（单槽，因为每次都是全量快照），在 online / 切回前台 / 下次启动 / 下次保存时重试，成功才清除。</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>新增 E2E 用例1（注入发送失败 → 断言留下待发副本+提示+状态；恢复后 online 触发重试 → 断言服务器真实收到新值，且读的是 /api/v1/state 而非 stub）；pytest 78 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>M-5</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>① 端到端脚本进 CI：用例0 + 完整输出 + 任一 FAIL 即非 0 退出</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>缺陷1 本可以被一条 E2E 用例当场抓住，但脚本只在个人机器上手跑 → 没有执行就没有防线。新增 backend/scripts/verify_mirror_e2e.js（用例0 冷启动整库写不得被守卫拒绝；用例1 失败不静默 + 重试送达），与 verify_decision_log.js 一起接入 .github/workflows/ci.yml 的新 e2e 作业（windows-latest 自带 Edge；固定 Node 22 因为脚本用全局 WebSocket；自己起后端并轮询就绪；不做任何输出截断）。</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>本机以**空库**（= CI 场景，全新 SQLite）复跑两个脚本：镜像 7 项断言全 PASS、决策日志 PASS，退出码均为 0；空库下 GET /state 只有 14 键且 ashTarget 为 null，基线逻辑已适配</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>M-6</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>
       </c>
     </row>
@@ -3022,4 +3167,166 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>浏览器→服务器镜像链路：三个缺陷的共同根因与可复用的判据（2026-09-11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>事实</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>为什么会长期没被发现</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>可复用的判据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>共同根因</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>三个缺陷（守卫误拒 / keepalive 超限 / 镜像洗样本）都发生在**同一条写路径**上，而该路径末尾是 .catch(() =&gt; {})：任何失败都只表现为「服务器没收到」，前端界面完全正常。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>镜像被设计成「尽力而为的副本」，于是「失败」在当时看起来是允许的；但「允许失败」不等于「允许不报告失败」——前者是可用性取舍，后者是失去了观测能力。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>写路径必须区分「尽力而为」（可失败）与「静默」（不可接受）：失败至少要有状态、计数或提示之一。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>准入 vs 所有权</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>M-1 只收窄了守卫的比较范围，没收窄镜像的写入范围 → 放行之后整库覆盖立刻洗掉了服务器的 heavy_samples（M-3）。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>修复一条链路时注意力在「让请求通过」，而「通过之后会写什么」是另一个方向的问题；回归用例当时只断言「写入被接受」，没有断言「接受后各表的内容」。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>改了「准入条件」必须同时检查「写入所有权」；回归断言要覆盖**写入结果**，不能只覆盖**是否放行**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>空转的测试</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>M-6：E2E 的探针值恰好与遗留值相同 → 新快照与上次已发送内容逐字节相同 → 被「内容相同则跳过」短路，断言在遗留状态上全绿。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>断言只检查了「最终状态对不对」，没有检查「这一步到底有没有发生」；而「没发生」和「发生了且正确」在只看终态时无法区分。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>每个用例都要有一条「这一步确实执行了」的断言（调用计数/副作用），并且输入必须与初始状态**可证明地不同**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>用 stub 验证被 stub 掉的层</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>早期验证把 Api.putStateBody 打桩后断言调用次数，而真正坏掉的正是这一层的实现，于是得到「22 → 2，看起来很好」的错误绿灯。</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>打桩让测试更容易通过，恰好绕过了唯一出问题的地方。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>只允许用打桩**注入失败**，不允许用打桩**替代成功路径**；成功路径必须走真实网络并回读服务器状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>没有执行就没有防线</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>M-1 的缺陷本可以被一条 E2E 用例当场抓住，但该脚本只在个人机器上手跑，长期无人执行。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>手工脚本的「可用性」依赖个人自觉，而自觉不是机制。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>能进 CI 的必须进 CI；跑不动的（依赖生产库数据的对拍）要写明「何时必须手跑」，并把输出完整保留（截断会藏掉 FAIL 行）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -15,6 +15,7 @@
     <sheet name="暂缓项与原因" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="第二轮审查意见" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="同步链路缺陷复盘" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="写路径评审与修复" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2187,7 +2188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2490,6 +2491,38 @@
       <c r="F11" s="12" t="inlineStr">
         <is>
           <t>【已决 2026-09-10：暂缓，并写明触发条件】T-9（自定义日期格式对拍）与 T-4（导入 golden）已落地，**迁移的前置护栏已经具备**，所以这不再是风险问题、纯粹是收益/时机问题。触发条件：出现第二个需要导 Excel 的人/机器，或浏览器解析出一次实际事故。另注：/import/parse 仍是半成品端点（无调用者 + 按 Sheet 合并的逻辑与浏览器不同源），其畸形日期崩溃已修；若半年内不迁移就删掉，别让它长期以「看似可用」的状态存在。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Q-9</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>待决</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>整库镜像对 manual_entries / import_logs / alerts / coarse_models 的**所有权**（2026-09-11 由独立评审 + 实测确认）</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>migrate.replace 对 force=False 也会 wipe 并重写这些表，而防回退守卫**不保护**它们（刻意排除，因为前端「清空补录历史」会合法地让它们变少）。同时前端只用到 GET /state、PUT /state、POST /training/coarse-model —— **整库镜像就是浏览器侧补录/导入日志/告警上行的唯一通道**。于是形成风险：某个浏览器手里的列表比服务器短（另一台浏览器新增过、或本地被清过），它的一次镜像就会把服务器上的那些行**静默删掉**（守卫不拦）。</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>方案A 维持现状（单浏览器使用假设）：成本 0，风险=多浏览器/清库场景下静默丢这些行；方案B 守卫扩展到这些表 + 显式清空走 force=true：需要前端把「我确实清空了」作为显式意图上报；方案C 前端改为逐条调用 POST /manual-entries 等接口，镜像不再拥有这些表：最干净，但要新增前端调用与错误处理（工作量中等）；方案D 服务器对这些表改为「按 ts 合并、只增不删」。</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>建议先做方案B 的最小版：把 alerts / import_logs 纳入守卫（它们没有「用户清空」的需求），manual_entries 保留「显式清空」入口后再纳入。实测证据：前端种子 seed_data.js 里 manualEntries=242 / importLogs=3 / alerts=0，而服务器库是 242 / 3 / 1（两侧本就不同步，本轮 E2E 没造成损失只因种子里恰好有同样的 242 条，属运气不是机制）。</t>
         </is>
       </c>
     </row>
@@ -3329,4 +3362,276 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>独立评审（只读、未运行脚本）对镜像写路径改动的发现与处置（2026-09-11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>严重度</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>发现</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>处置与证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>R-1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>api.js 把**任何** ok:false 都判为 rejected，而后端 migrate.replace 的 except 分支（如 SQLite 写锁超时）同样返回 ok:false 但没有 stale → 服务器**瞬时**异常被当成「永久拒绝、不留副本不再重试」，正是这次要根除的静默丢失被固化成设计。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>已改为 `rejected: j.stale === true`，其余 ok:false 归入可重试的传输/瞬时失败。证据：migrate.py:319-321 的 except 分支只返回 {ok:false,error}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>待发副本只在 promise 回调里写：页面关闭/切后台时那次请求被浏览器中断，回调永不执行 → **「关页面丢最后一笔」这个原始痛点其实没解决**；且槽里若残留更旧快照，下次启动会把它推回服务器（守卫只比条数，可能放行）。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>已改为**发送前**先落副本（语义：本地已保存、服务器未确认），成功或被守卫拒绝后再清。E2E 新增断言 slotRightAfterSend（发送返回前槽里就必须有内容）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R-3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>keepalive 上限用 body.length（字符）去卡 64 KiB（字节）：整库快照以中文为主，JSON.stringify 不转义非 ASCII，1 字符 = 3 字节 → 以为装得下、实际 3 倍超限，缺陷B（keepalive 超限 → TypeError）原样残留。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>改用 Blob([body]).size 取**字节数**，阈值降到 48 KB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>R-4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>E2E 用例0 在 CI 必然**空转假 PASS**：守卫是 `if sum(current.values()) &gt; 0 and regressed`，空库上直接关闭；而 CI 的库必然是空的（*.db 被 gitignore）。即：即使把 heavy_samples 加回守卫，用例0 也照样绿。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>已改为先播种（records + samples/heavy-ash）并断言 GUARD_ARMED；并做了**反向对照**：临时把 heavy_samples 加回守卫后重跑，MIRROR_COLD_START 立刻 FAIL（stale_store ... heavy_samples 0&lt;1），撤销后恢复 PASS —— 证明用例0 真的有牙齿，而不是只会绿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R-5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>E2E 脚本对着**真实开发库**跑是破坏性的：整库 PUT 会 wipe/重写 manual_entries/alerts/import_logs/coarse_models/settings/auto_state，而脚本只复原了 ashTarget。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>已加前置检查：目标库非空则**直接拒跑**（退出码 2）并说明原因，需显式 DMCS_ALLOW_REAL_DB=1 放行。另新增 MIRROR_KEEPS_HEAVY_SAMPLES 断言（没有 GET 采样接口，用「新插入的自增 id 是否在原 id 之后」判断表没被清空）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>R-6</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>用例1 只覆盖传输失败，新的 rejected 分支零覆盖；且 MIRROR_RETRY_ON_ONLINE 只断言结果、不断言因果（任何一次成功都能满足）。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>新增用例2（注入 rejected：必须不留待发副本、记 rejected 计数、给 info 提示、内容相同的再次保存不得重发）；新增 MIRROR_NOT_DELIVERED_YET 断言（注入失败后服务器必须仍是基线值），让「重试送达」具备因果前提。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>R-7</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>跨标签页会丢数据：待发槽是裸 body、无归属无时间戳，成功时无条件清除 → B 标签页的成功会删掉 A 标签页尚未送达的唯一副本；旧标签页的失败还会覆盖新快照。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>槽内结构改为 {wall, stamp, body}：写入时若已有更新的快照则不覆盖（wall），清除时只清自己写的那份（stamp）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>R-8</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>rejected 分支不清槽、不更新 _mirrorSent → 每次 online/切前台都会重发一次注定被拒的整库；提示语「正在自动反向同步」是假的（autoPullIfStale 只在启动跑一次）。</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>rejected 现在会清掉自己那份副本、记入 _mirrorSent（内容不变不再重发），并在失败 streak 的第一次**真的**调用 autoPullIfStale()，让提示语成真。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>R-9</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>CI：e2e 作业无 timeout-minutes（默认挂 360 分钟）、就绪探测号称 60 秒实际更久、Edge 候选三处不一致、无收尾步骤（自托管会留僵尸占端口）。</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>已加 timeout-minutes: 15、短超时探针 + 真实计时输出、Edge 候选统一为同一份列表、新增 if: always() 的停后端步骤。另把两个脚本的 CDP 端口改为随机，避免连到遗留浏览器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>去重判据位置不对：saveStore 每次都会置 _mirrorPending，而「内容与上次已发送相同则跳过」只在「内容来自槽」时生效 → 正常保存路径上的重复内容永远会重发（被守卫拒绝的整库会被反复重发）。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>判据提到「看来源之前」。E2E 用例2 断言第二次相同保存不增加发送次数（实测 _mirrorStats.skippedSame 由 0 → 1）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>建议先做方案B 的最小版：把 alerts / import_logs 纳入守卫（它们没有「用户清空」的需求），manual_entries 保留「显式清空」入口后再纳入。实测证据：前端种子 seed_data.js 里 manualEntries=242 / importLogs=3 / alerts=0，而服务器库是 242 / 3 / 1（两侧本就不同步，本轮 E2E 没造成损失只因种子里恰好有同样的 242 条，属运气不是机制）。</t>
+          <t>【2026-09-11 修正：原先建议的方案B 经实现前核查**不成立**，已撤回】关键事实：GET /api/v1/state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / regressionModels / heavySamples —— 浏览器永远拿不到服务器上的这些行；而后端除 /manual-entries 的 POST（前端无调用者）外没有任何地方写 Alert / ImportLog，这些表**只由浏览器整库镜像写入**。把这类表纳入守卫，等于让守卫去比较一个两端**不可能收敛**的集合：只要某台浏览器的列表比服务器短，它的每一次镜像都会被拒，而它永远无法通过 GET 补上缺失的行 → **永久拒写**，正是缺陷 M-1 的病理。alerts 还更特殊：checkAlerts() 每次刷新都重建该数组（派生值，合法变少），纳入守卫会在告警消失时立刻开始拒写。另注：force=true 会连 heavy_samples 一起整体重写，所以「显式清空走 force」在支持**按表 force** 之前也不能直接用。因此可行的是方案C（前端逐条上行，镜像不再拥有这些表）或方案D（服务器只增不删/按 ts 合并）。</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3607,22 +3607,44 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>（我自己上一版的建议错了，实现前核查时发现）曾建议「方案B：把 alerts / import_logs 纳入防回退守卫」。但 GET /state 不返回这两张表，浏览器永远拿不到服务器上的行，而它们只由整库镜像写入 —— 纳入守卫会让「列表较短」的浏览器**永久拒写**（守卫比较两端不可能收敛的集合），即缺陷 M-1 的病理；alerts 还是每次刷新重建的派生数组。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>已**撤回该建议**并写入 Q-9 的修正说明。教训：判断「某表能不能进守卫」的标准不是「它会不会被用户清空」，而是「两端能否收敛」——守卫只能比较双方都能拿到同一份数据的集合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>去重判据位置不对：saveStore 每次都会置 _mirrorPending，而「内容与上次已发送相同则跳过」只在「内容来自槽」时生效 → 正常保存路径上的重复内容永远会重发（被守卫拒绝的整库会被反复重发）。</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>判据提到「看来源之前」。E2E 用例2 断言第二次相同保存不增加发送次数（实测 _mirrorStats.skippedSame 由 0 → 1）。</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
+          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1547,7 +1547,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-6）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-7）</t>
         </is>
       </c>
     </row>
@@ -2014,22 +2014,44 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>M-7</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>
@@ -2522,7 +2544,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>【2026-09-11 修正：原先建议的方案B 经实现前核查**不成立**，已撤回】关键事实：GET /api/v1/state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / regressionModels / heavySamples —— 浏览器永远拿不到服务器上的这些行；而后端除 /manual-entries 的 POST（前端无调用者）外没有任何地方写 Alert / ImportLog，这些表**只由浏览器整库镜像写入**。把这类表纳入守卫，等于让守卫去比较一个两端**不可能收敛**的集合：只要某台浏览器的列表比服务器短，它的每一次镜像都会被拒，而它永远无法通过 GET 补上缺失的行 → **永久拒写**，正是缺陷 M-1 的病理。alerts 还更特殊：checkAlerts() 每次刷新都重建该数组（派生值，合法变少），纳入守卫会在告警消失时立刻开始拒写。另注：force=true 会连 heavy_samples 一起整体重写，所以「显式清空走 force」在支持**按表 force** 之前也不能直接用。因此可行的是方案C（前端逐条上行，镜像不再拥有这些表）或方案D（服务器只增不删/按 ts 合并）。</t>
+          <t>【2026-09-11 修正：原先建议的方案B 经实现前核查**不成立**，已撤回】关键事实：GET /api/v1/state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / regressionModels / heavySamples —— 浏览器永远拿不到服务器上的这些行；而后端除 /manual-entries 的 POST（前端无调用者）外没有任何地方写 Alert / ImportLog，这些表**只由浏览器整库镜像写入**。把这类表纳入守卫，等于让守卫去比较一个两端**不可能收敛**的集合：只要某台浏览器的列表比服务器短，它的每一次镜像都会被拒，而它永远无法通过 GET 补上缺失的行 → **永久拒写**，正是缺陷 M-1 的病理。alerts 还更特殊：checkAlerts() 每次刷新都重建该数组（派生值，合法变少），纳入守卫会在告警消失时立刻开始拒写。另注：force=true 会连 heavy_samples 一起整体重写，所以「显式清空走 force」在支持**按表 force** 之前也不能直接用。因此可行的是方案C（前端逐条上行，镜像不再拥有这些表）或方案D（服务器只增不删/按 ts 合并）。【已决 2026-09-11：采用方案D 并已实现】migrate.replace 对 force=False 不再 wipe 这些表，改为按自然键合并（manual_entries: ts+category；import_logs: ts+category+filename；alerts: ts+system+message；regression_models: model_type+created_at；coarse_model_history: trained_at+production），只插入库里没有的行、**不删除**任何已有行；force=true（备份恢复）仍是整体覆盖。真实库实证：发送 manualEntries/alerts/importLogs 全为空的镜像后，服务器的 manual_entries 242 / alerts 1 / import_logs 3 **一条不少**。代价（已知并接受）：界面「清空补录历史」不再删除服务器侧历史行——若要在界面上真正清服务器，需要单独的 force 入口（见 M-7 的后续项）。</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3607,44 +3629,66 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R-12</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>方案D 的代价：镜像不再删除这些表 → 界面「清空补录历史」只清本地，服务器侧历史行会保留（用户从界面看不出来，因为 GET /state 本来就不返回这些表）。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>已在 Q-9 与 M-7 写明。后续项：给「清空补录历史」加文案说明，或加一个显式的「同时清除服务器历史（force）」入口——这需要按表 force（现在 force=true 会连 heavy_samples 一起整体重写）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>R-11</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>（我自己上一版的建议错了，实现前核查时发现）曾建议「方案B：把 alerts / import_logs 纳入防回退守卫」。但 GET /state 不返回这两张表，浏览器永远拿不到服务器上的行，而它们只由整库镜像写入 —— 纳入守卫会让「列表较短」的浏览器**永久拒写**（守卫比较两端不可能收敛的集合），即缺陷 M-1 的病理；alerts 还是每次刷新重建的派生数组。</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>已**撤回该建议**并写入 Q-9 的修正说明。教训：判断「某表能不能进守卫」的标准不是「它会不会被用户清空」，而是「两端能否收敛」——守卫只能比较双方都能拿到同一份数据的集合。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>去重判据位置不对：saveStore 每次都会置 _mirrorPending，而「内容与上次已发送相同则跳过」只在「内容来自槽」时生效 → 正常保存路径上的重复内容永远会重发（被守卫拒绝的整库会被反复重发）。</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>判据提到「看来源之前」。E2E 用例2 断言第二次相同保存不增加发送次数（实测 _mirrorStats.skippedSame 由 0 → 1）。</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -16,6 +16,7 @@
     <sheet name="第二轮审查意见" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="同步链路缺陷复盘" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="写路径评审与修复" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="写接口鉴权与事故复盘" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -652,7 +653,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
+          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）；M-8 写接口鉴权（token + force 限本机，局域网实测 + 真实浏览器实测）；M-9 一次 force 清库事故与完整恢复；M-10 force 前自动备份与工具纪律。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
         </is>
       </c>
     </row>
@@ -695,6 +696,190 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>写接口访问控制（M-8）与一次 force 清库事故的复盘（M-9/M-10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>事实</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>为什么</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>可复用的判据 / 后续动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>威胁模型</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>服务 bind 0.0.0.0，此前所有写接口零鉴权：同网段任意主机可整库覆盖/清空。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>系统一直当「内网可信」用，而实际暴露面是整个局域网（含访客设备等）。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>读写分级：读接口保持开放（现场看板要方便）；写接口要 token；**整库覆盖（force）只许本机** —— 破坏性与非破坏性必须不同级别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>为什么 token 随页面下发</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>token 随首页 &lt;meta&gt; 下发，浏览器零配置；本机回环免 token。</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>现场操作员不该被要求输密码；而脚本/E2E 都从本机跑，免 token 不影响工具链。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>诚实边界：能打开页面的人能读到 token —— 这挡的是**盲扫脚本与误操作**，不是「有浏览器的人」。真要防内部人员，需要账号体系（另立需求）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>事故经过</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>为验证「回环 force 放行」，我的核对脚本向**真实库**发了空 store + force=true，11 张表被清空（529 条记录、242 条补录等）。</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>验证脚本把生产库当成测试对象 —— 而 force 的设计就是「绕过一切守卫」。更根本的是：破坏性操作当时**没有任何撤销手段**。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>① 破坏性验证只对临时库；② 破坏性接口必须自带撤销（M-10 的自动备份）；③ 脚本里凡是要发 force，先确认目标库是临时库（参照 verify_mirror_e2e.js 的非空库拒跑）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>恢复过程</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>停服务防 checkpoint → 快照 db/-wal/-shm → 解析 WAL 帧与提交边界 → 发现删除前的页镜像仍在主库文件（15:37 的 checkpoint），WAL 里只有删除后的写入 → 丢弃 WAL → 逐表核对全部一致（529/242/3/1/2/1/8/11）。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>WAL 模式下「当前状态」是主库文件 + WAL 叠加；只有 WAL 被 checkpoint 后主库才会被覆盖。事故与上一次 checkpoint 之间的窗口保住了数据。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>**这是运气不是机制**：若删除发生在 checkpoint 之后，旧页就会被覆盖。所以 M-10 的备份不是锦上添花，而是把运气换成机制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>工具纪律</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>本次还有一处 patch 因锚点不符而**静默未生效**（api.js 的 token header 注入），是 E2E 断言把它抓出来的；备份文件名第一版秒级时间戳会撞名覆盖回滚点，是测试的回滚演练断言抓出来的。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>静默失败的补丁与静默失败的写入是同一类问题：**看起来做了，其实没做**。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>① 每次字符串替换都要断言命中次数；② 关键行为必须有断言覆盖；③ 测试要包含一次真实回滚演练，而不是只断言「文件存在」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>事故后仍待办</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>token 挡住了盲扫，但**能打开页面的人仍能正常写入**（含覆盖 settings/auto_state）；数据库文件本身无加密；备份仅保留在本机。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>单机现场系统的合理边界，先解决「外部人一键清库」，账号体系与异地备份属于下一步。</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>若需要多用户/责任到人：加账号 + 操作审计（决策日志已有雏形）；定期把 backups/ 与导出文件复制到第二台机器。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1535,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1547,7 +1732,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-7）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-10）</t>
         </is>
       </c>
     </row>
@@ -2016,42 +2201,108 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>M-8</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>M-9</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -17,6 +17,7 @@
     <sheet name="同步链路缺陷复盘" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="写路径评审与修复" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="写接口鉴权与事故复盘" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="实测密度计(仅展示)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,7 +654,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）；M-8 写接口鉴权（token + force 限本机，局域网实测 + 真实浏览器实测）；M-9 一次 force 清库事故与完整恢复；M-10 force 前自动备份与工具纪律。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
+          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）；M-8 写接口鉴权（token + force 限本机，局域网实测 + 真实浏览器实测）；M-9 一次 force 清库事故与完整恢复；M-10 force 前自动备份与工具纪律；M-11 新增「实测密度计」（仅展示：两个界面 + Δ 偏差，不参与任何计算）。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
         </is>
       </c>
     </row>
@@ -874,6 +875,212 @@
       <c r="D9" s="9" t="inlineStr">
         <is>
           <t>若需要多用户/责任到人：加账号 + 操作审计（决策日志已有雏形）；定期把 backups/ 与导出文件复制到第二台机器。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>新增「实测密度计」：为什么只做展示、展示在哪、以后怎么升级为权威值</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>议题</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结论 / 做法</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>以后要改的话怎么做</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>为什么必须做</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>现场已知在线密度计存在测量误差，需要一个人工实测值作对照。</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>没有对照就只能凭经验判断在线值准不准；有了两台表的差值，误差是可量化、可追踪的。</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>为什么不接进计算</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>**仅展示**：不参与建议密度、灰分公式、模型、任何报警判定。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>密度指导按总灰分线性指导 —— 它只对「需要调整多少(Δρ)」敏感，对密度计读数绝对值不敏感（读数只出现在展示与决策日志的 ρ旧 里）。换句话说：把哪台表的值喂进去，系统行为都一样，所以接进计算只会增加耦合与误解风险。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>真要把实测值当权威值：把 resolveDensity() 改为读 density_actual（一处），并同步密度指导里 rhoCur 的来源与决策日志的 ρ旧 口径；建议等积累一段两台表的偏差数据后再定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>值从哪来</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>双击手动录入 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认值**。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>实测值只应来自人工。给它一个「仪表默认值」（例如取在线值）会让人分不清哪条是真实测，以后做偏差分析时会得出「两台表完全一致」的假结论。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>若将来接了第二台在线密度计，再加一层「仪表自动值」，并标明来源为「在线(实测表)」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>展示在哪</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>① 采集页「在线仪表实时数据」表新增一行（未录入显示 —，来源列显示 手动/录入/未录入）；② 总览页「合并系统」卡片新增「实测密度」并显示 Δ（与在线密度计之差），|Δ|&gt;0.02 标黄。</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>两个位置分别对应两种使用场景：采集页是录入与看原始值的地方；合并系统卡片是操作员做决策时看的那一眼，偏差直接决定「要不要信在线值」。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>若要加历史趋势：把实测值也在趋势图上画一条线（需要先决定它与「各系统灰分趋势」共图还是单图）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>输入校验</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>1.30~1.65 之外**拒收**（提示并拒绝）；1.35~1.60 之外但在硬限内 → 质量状态标黄「偏离」。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>硬限挡手滑（少打/多打一位）；软限对应正常分选密度区间，越界未必是错，但要提醒核对。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>现场若实际分选密度长期超出 1.35~1.60，改 App.DENSITY_ACTUAL 的 softMin/softMax 即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>记录到哪</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>localStorage（主存储）→ 整库镜像 → auto_state.instrumentInputs；补录同时进 calcLogs(density_actual) 与 manualEntries；密度决策日志 ctx 增记 densityActual，导出表加「实测密度」列。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>镜像与 backfill 都走既有通道，无需新增后端表或接口；ctx 记录使得「当时实测是多少」在事后可查 —— 这是以后标定在线密度计的唯一数据来源。</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>如果要按小时/班次统计偏差，需要把实测值也写进简报（brief）：那要动后端 brief.py 与前端简报页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>自动化守卫</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>backend/scripts/verify_density_actual.js（13 项断言，已进 CI）。</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>其中 CALC_UNAFFECTED 断言「设置实测密度前后所有计算结果逐项一致」——它是「仅展示」这个承诺的机器守卫，避免以后有人顺手把它接进计算。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>若将来确实要升级为权威值，这条断言要**有意识地**改掉，并在提交说明里写明理由。</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1732,7 +1939,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 同步链路 M-1~M-10）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 M-1~M-11）</t>
         </is>
       </c>
     </row>
@@ -2199,110 +2406,137 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>M-8</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>M-11</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-9</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）；M-8 写接口鉴权（token + force 限本机，局域网实测 + 真实浏览器实测）；M-9 一次 force 清库事故与完整恢复；M-10 force 前自动备份与工具纪律；M-11 新增「实测密度计」（仅展示：两个界面 + Δ 偏差，不参与任何计算）。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
+          <t>同步链路（浏览器→服务器镜像）专项：M-1 守卫误拒（自 ca08e85 起同步实际已全死）、M-2 keepalive 64 KiB 上限、M-3 镜像洗掉服务器化验样 三个缺陷修复；M-4 写路径禁止静默吞错（结果返回 + 待发副本 + 守卫拒绝/传输失败两类分开处置）；M-5 端到端脚本进 CI（用例0 冷启动写不得被拒 + 失败不静默 + 重试送达，另含密度决策日志链路）；M-6 E2E 自身空转假 PASS 的教训与修法；M-7 方案D：镜像对浏览器收不到的表只增不删（真实库实证不掉一行）；M-8 写接口鉴权（token + force 限本机，局域网实测 + 真实浏览器实测）；M-9 一次 force 清库事故与完整恢复；M-10 force 前自动备份与工具纪律；M-11 新增「实测密度计」（仅展示：两个界面 + Δ 偏差，不参与任何计算）；M-12 第二次数据损失与根因修复（快照只拥有它携带的表）。**共同根因是 .catch(()=&gt;{}) 吞掉了全部失败**；pytest 78 全绿，空库（CI 场景）两个 E2E 脚本 PASS。</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -857,22 +857,67 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>第二次事故
+(2026-09-11/12)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>为验证 force 前置备份，把 GET /state 的结果**原样 force 写回**；GET 不返回 manualEntries/importLogs/alerts/coarseModelHistory/heavySamples，force 又是整库删空再重写 → 这几张表被清空（242/3/1/1 → 0）。</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>上一次事故后我把注意力放在「别对着生产库发破坏性请求」，却漏了更隐蔽的一类：**看起来无害的原样写回**也可能具有破坏性 —— 因为快照并不携带全部表。与 M-9 同根：把「缺键」当成了「空表」。</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>判据（已写进 migrate.py 注释与用例）：**快照只拥有它携带的表**。凡「读出来再写回去」的操作，先问一句：这个快照带全了吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>根因修复与验证</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>migrate.replace 的写入范围改由载荷键决定（TABLE_OWNER_KEYS）；settings/auto_state 只按携带的键 upsert；响应新增 owned / untouched。</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>修「操作纪律」只能防我一个人，修「接口语义」才能防所有人（包括以后的我、脚本、别的 agent）。</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>回归用例 test_force_get_payload_roundtrip_is_not_destructive 直接重演事故操作；并在**生产库**上重演同一条命令：写回前后 manual_entries 242 / import_logs 3 / alerts 1 / coarse_model_history 1 全部未变（owned=[calc_logs, coal_records, coarse_models]，untouched 里列出其余表）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>事故后仍待办</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>token 挡住了盲扫，但**能打开页面的人仍能正常写入**（含覆盖 settings/auto_state）；数据库文件本身无加密；备份仅保留在本机。</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>单机现场系统的合理边界，先解决「外部人一键清库」，账号体系与异地备份属于下一步。</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>若需要多用户/责任到人：加账号 + 操作审计（决策日志已有雏形）；定期把 backups/ 与导出文件复制到第二台机器。</t>
         </is>
@@ -1927,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1939,7 +1984,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11 M-1~M-11）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11/12 M-1~M-12）</t>
         </is>
       </c>
     </row>
@@ -2406,137 +2451,159 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>M-12</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>M-11</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>M-8</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-9</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1984,7 +1984,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11/12 M-1~M-12）</t>
+          <t>本轮已完成事项与验证证据（2026-09-10 批次 0-2 · 2026-09-11/12 M-1~M-14）</t>
         </is>
       </c>
     </row>
@@ -2451,159 +2451,203 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>M-12</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>M-13</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>重介精煤灰分加「手动/计算」来源选择（2026-09-12 需求）</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>现场需求：密度计应能影响重介精煤灰分，但此前只要手动填过重介灰分，它就**永久压住**计算值 —— 全项目没有任何地方给重介灰分打「自动层时间点」（_autoBump('heavyAsh') 不存在），而其它仪表（皮带秤/灰分仪/液位）都有该机制。于是「把密度计调到建议值 → 重介灰分变化 → 总灰分达标」这条链走不通。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>实现在在线仪表的重介精煤灰分行加下拉（与总精煤灰分同款）：手动=用填写的化验值；计算=502在线值 + 密度仿真（密度计因此在起作用）。默认按「升级前有手动值就是手动优先」迁移，不悄悄改变现场行为；双击填值自动切到手动（避免「填了却不生效」）；「总灰分修改」开启时该下拉随公式因素一并冻结；手动档下并列显示「计算 X.XX」供对照；决策日志 ctx 增记 heavyAshSource，导出表加「重介灰分来源」列。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>M-11</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>M-14</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>闭环增益不一致（M-13 验证时量化出来的，**待决策**）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>把重介灰分切到「计算」后按建议密度调整，灰分**方向正确但过冲约 1.74 倍**。实测：仿真+配煤公式的增益 = 28.91% 总灰分/单位密度（0.01 密度 → 0.2891% 总灰分）；而专家表第一档（0.15% → 0.01 g/cm³）隐含的增益只有 15%/单位密度 → 步长偏大约 1.93 倍。</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>三个选项：① 不动专家表（承认一次调整会过冲，现场建议小步或分两次）；② 把仿真常数 simK 由 0.03 调到约 0.058，使其与专家表隐含增益一致（改的是仿真口径，501/502 在线显示值会随之变化）；③ 建议密度改成「基于增益的一步补偿」（Δρ = ΔA / 增益，增益由链路算出）并保留钳制与死区 —— 最准，但改的是核心建议算法。注意：这三条都只让**仿真闭环**自洽；真实过程增益仍需现场阶跃实验标定（K 标定那条线）。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>M-8</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
+          <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
+          <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
+          <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>M-9</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>M-11</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>M-9</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -2480,17 +2480,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>闭环增益不一致（M-13 验证时量化出来的，**待决策**）</t>
+          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>把重介灰分切到「计算」后按建议密度调整，灰分**方向正确但过冲约 1.74 倍**。实测：仿真+配煤公式的增益 = 28.91% 总灰分/单位密度（0.01 密度 → 0.2891% 总灰分）；而专家表第一档（0.15% → 0.01 g/cm³）隐含的增益只有 15%/单位密度 → 步长偏大约 1.93 倍。</t>
+          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>三个选项：① 不动专家表（承认一次调整会过冲，现场建议小步或分两次）；② 把仿真常数 simK 由 0.03 调到约 0.058，使其与专家表隐含增益一致（改的是仿真口径，501/502 在线显示值会随之变化）；③ 建议密度改成「基于增益的一步补偿」（Δρ = ΔA / 增益，增益由链路算出）并保留钳制与死区 —— 最准，但改的是核心建议算法。注意：这三条都只让**仿真闭环**自洽；真实过程增益仍需现场阶跃实验标定（K 标定那条线）。</t>
+          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
         </is>
       </c>
     </row>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2451,208 +2451,235 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>M-15</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>按现场访谈答案改专家表口径（2026-09-12）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>访谈三问的答案：① 偏差 0.15%→0.01、0.30%→0.02、**最多 0.03**；② 口径 = **总精煤灰分**；③ 密度最小可设 **0.005 甚至更小**。结论：现场做法 = **比例律（≈1/15 g/cm³ 每 1% 灰分）+ 封顶 0.03**，既不是纯增益律（大偏差不按比例）、也不是纯步长限幅（小偏差确实按比例）。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>改动：专家表由「0.15→0.01、0.25→0.02、斜率 0.1 无上限」改为 **Δρ = min(|ΔA|/15, 0.03)**（死区 0.05 不变），前后端同步。旧表的问题：1.5% 偏差时给 0.145 = 现场上限的 4.8 倍；0.30% 时给 0.025 而现场是 0.02；斜率 0.1 与现场的 0.067 不符。口径确认（Q2）说明现有 deltaA 实现正确、无需改换算；Q3 说明执行器分辨率足够细，死区 0.05 与增益 15%/单位相容（半步响应 0.0375 &lt; 0.05），不必为抗极限环放宽死区。仍待定一项：建议的**单次步长上限**取 0.01/0.02/0.03（现为界面「钳制」=0.01，最保守）。</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>pytest 102 全绿（含 2 条改写后的专家表用例：0.25→1/15、1.5→封顶 0.03）；简报 golden 已按前端重新生成并通过前后端逐值对拍（证明两侧新口径一致）；verify_heavy_ash_source.js 14 项断言全 PASS（逐步 3 步收敛、棘轮已停、仿真门控/限幅、占位值守卫）；docs/密度增益标定-现场访谈提纲.xlsx 已填入答案并新增「访谈结论（2026-09-12）」Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>M-13</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>重介精煤灰分加「手动/计算」来源选择（2026-09-12 需求）</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>现场需求：密度计应能影响重介精煤灰分，但此前只要手动填过重介灰分，它就**永久压住**计算值 —— 全项目没有任何地方给重介灰分打「自动层时间点」（_autoBump('heavyAsh') 不存在），而其它仪表（皮带秤/灰分仪/液位）都有该机制。于是「把密度计调到建议值 → 重介灰分变化 → 总灰分达标」这条链走不通。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>实现在在线仪表的重介精煤灰分行加下拉（与总精煤灰分同款）：手动=用填写的化验值；计算=502在线值 + 密度仿真（密度计因此在起作用）。默认按「升级前有手动值就是手动优先」迁移，不悄悄改变现场行为；双击填值自动切到手动（避免「填了却不生效」）；「总灰分修改」开启时该下拉随公式因素一并冻结；手动档下并列显示「计算 X.XX」供对照；决策日志 ctx 增记 heavyAshSource，导出表加「重介灰分来源」列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>M-14</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>M-14</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>M-12</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>M-11</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>M-8</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-9</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2451,235 +2451,262 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>M-16</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>单次步长上限默认 0.02 + 把仿真增益标定到现场确认值（2026-09-12）</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>① 步长上限：现场「大多数是 0.01、0.02，最多 0.03」，系统原先发布上限取界面「钳制」默认 0.01（0.03 要分 3 步走）→ 默认改 **0.02**（覆盖大多数情形一步到位、仍低于 0.03 上限；界面随时可改），并对老 store 里存的旧默认 0.01 做一次性迁移（用户自己设过的其它值不动）。② 仿真增益标定：E2E 实测出仿真增益 28.91%/单位 = 现场确认值 15%/单位的 **1.93 倍**，于是按现场口径定的 0.02 步长在仿真里会越过目标、衰减很慢。会诊当时否决过「把 simK 调到与专家表一致」（理由是两个常数都没依据、互相对齐是循环标定），但**这个前提已经变了**：15%/单位是现场确认过的，所以按它反推 simK 是标定而非循环 ——simK = 配煤权重 0.867 / 15 ≈ **0.0578**。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>改动：app.js / density.py 的 simK 0.03 → 0.0578（含「P3 实测后用实测值替换」的注释）；同时把仿真项镜像进后端 resolvers.resolve_instrument（此前只有前端有 → 同一份 store 两侧取值不同，简报与卡片会对不上），含同样的门控（只在密度有真实来源时叠加）与限幅 ±1.0。测试期望同步：逐步用例改为 0.02 步长（rhoNew 1.47）；E2E 收敛判据恢复为「不越零 + ≤6 步」。</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>pytest 102 全绿；verify_heavy_ash_source.js **14 项全 PASS**，关键输出：实测增益 **15%/单位密度**（与现场一致，步长偏大 1.00 倍）；逐步闭环 **2 步收敛**（偏差 0.499% → 0.199% → 0.004%，不越零）；棘轮已停；仿真门控（默认密度不再有幻象）；限幅 ±1.0；占位值守卫</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>M-15</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>按现场访谈答案改专家表口径（2026-09-12）</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>访谈三问的答案：① 偏差 0.15%→0.01、0.30%→0.02、**最多 0.03**；② 口径 = **总精煤灰分**；③ 密度最小可设 **0.005 甚至更小**。结论：现场做法 = **比例律（≈1/15 g/cm³ 每 1% 灰分）+ 封顶 0.03**，既不是纯增益律（大偏差不按比例）、也不是纯步长限幅（小偏差确实按比例）。</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>改动：专家表由「0.15→0.01、0.25→0.02、斜率 0.1 无上限」改为 **Δρ = min(|ΔA|/15, 0.03)**（死区 0.05 不变），前后端同步。旧表的问题：1.5% 偏差时给 0.145 = 现场上限的 4.8 倍；0.30% 时给 0.025 而现场是 0.02；斜率 0.1 与现场的 0.067 不符。口径确认（Q2）说明现有 deltaA 实现正确、无需改换算；Q3 说明执行器分辨率足够细，死区 0.05 与增益 15%/单位相容（半步响应 0.0375 &lt; 0.05），不必为抗极限环放宽死区。仍待定一项：建议的**单次步长上限**取 0.01/0.02/0.03（现为界面「钳制」=0.01，最保守）。</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>pytest 102 全绿（含 2 条改写后的专家表用例：0.25→1/15、1.5→封顶 0.03）；简报 golden 已按前端重新生成并通过前后端逐值对拍（证明两侧新口径一致）；verify_heavy_ash_source.js 14 项断言全 PASS（逐步 3 步收敛、棘轮已停、仿真门控/限幅、占位值守卫）；docs/密度增益标定-现场访谈提纲.xlsx 已填入答案并新增「访谈结论（2026-09-12）」Sheet</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>M-13</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>重介精煤灰分加「手动/计算」来源选择（2026-09-12 需求）</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>现场需求：密度计应能影响重介精煤灰分，但此前只要手动填过重介灰分，它就**永久压住**计算值 —— 全项目没有任何地方给重介灰分打「自动层时间点」（_autoBump('heavyAsh') 不存在），而其它仪表（皮带秤/灰分仪/液位）都有该机制。于是「把密度计调到建议值 → 重介灰分变化 → 总灰分达标」这条链走不通。</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>实现在在线仪表的重介精煤灰分行加下拉（与总精煤灰分同款）：手动=用填写的化验值；计算=502在线值 + 密度仿真（密度计因此在起作用）。默认按「升级前有手动值就是手动优先」迁移，不悄悄改变现场行为；双击填值自动切到手动（避免「填了却不生效」）；「总灰分修改」开启时该下拉随公式因素一并冻结；手动档下并列显示「计算 X.XX」供对照；决策日志 ctx 增记 heavyAshSource，导出表加「重介灰分来源」列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>M-14</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>M-14</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>M-12</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>M-11</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>M-8</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-9</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2453,260 +2453,287 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>M-17</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>把「终点」与「一次走多少」分开：新增建议密度（推测值）+ 经验范围提示（2026-09-12）</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>用户提出：建议密度目前只给人看、不影响生产，单步限幅（P0 逐步建议）是为**将来自动执行**准备的安全层；把「一次敢走多少」与「最终该落在哪」混成一个数，会让人看不到系统的判断终点。需求原话：密度计一步步每次调 0.01、最后落到 A，希望系统直接给出 A 作为建议密度（推测值），并放在首页卡片的隐藏卡片（点卡片弹出的计算详情）里。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>新增第三个量并各自标明含义：① 本次一步（≤界面钳制 0.02，人工/将来自动执行都用它）；② 法则完整修正 rhoTargetFull（现场法则封顶 0.03）；③ **建议密度（推测值）rhoPredict = clamp(ρ当前 − ΔA/15, 1.35, 1.60)** —— 偏差归零处的终点，不受法则封顶限制、只受物理范围限制，显示在卡片计算详情弹窗里。另加**经验范围提示**：|ΔA| 超过「法则封顶 0.03 × 增益 15 = 0.45%」时，推测值灰显并标注「超出经验范围，仅供参考；这么大的偏差现场做法是先查扰动源（换工作面/煤质/脱粉切换）而不是一次猛动密度」——阈值由常数相乘得出，法则或增益一变会随之变化。同时修正弹窗里过期的调整规则文案（原写「0.25%→0.02、按斜率 0.1 外推」）。</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>pytest 103 → **104 全绿**（新增经验范围用例：ΔA=0.30% 不标注、ΔA=1.10% 标注；以及推测值用例：ΔA=0.5% 时 deltaRho=−0.02 / deltaRhoFull=−0.03 / deltaRhoPredict=−0.0333（证明推测值确实不被法则封顶）、大偏差时被物理范围钳到 1.35）；verify_heavy_ash_source.js 15 → **16 项全 PASS**：PREDICT_TARGET_SHOWN（ρ=1.520、ΔA=0.499% → 推测值 1.487 = 1.52−0.499/15；法则完整修正 1.490；本次一步 1.500；弹窗已显示）与 PREDICT_RANGE_HINT（大偏差 1.349% → 标注；小偏差 0.439% → 不标注）；CI run 25 全绿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>M-16</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>单次步长上限默认 0.02 + 把仿真增益标定到现场确认值（2026-09-12）</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>① 步长上限：现场「大多数是 0.01、0.02，最多 0.03」，系统原先发布上限取界面「钳制」默认 0.01（0.03 要分 3 步走）→ 默认改 **0.02**（覆盖大多数情形一步到位、仍低于 0.03 上限；界面随时可改），并对老 store 里存的旧默认 0.01 做一次性迁移（用户自己设过的其它值不动）。② 仿真增益标定：E2E 实测出仿真增益 28.91%/单位 = 现场确认值 15%/单位的 **1.93 倍**，于是按现场口径定的 0.02 步长在仿真里会越过目标、衰减很慢。会诊当时否决过「把 simK 调到与专家表一致」（理由是两个常数都没依据、互相对齐是循环标定），但**这个前提已经变了**：15%/单位是现场确认过的，所以按它反推 simK 是标定而非循环 ——simK = 配煤权重 0.867 / 15 ≈ **0.0578**。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>改动：app.js / density.py 的 simK 0.03 → 0.0578（含「P3 实测后用实测值替换」的注释）；同时把仿真项镜像进后端 resolvers.resolve_instrument（此前只有前端有 → 同一份 store 两侧取值不同，简报与卡片会对不上），含同样的门控（只在密度有真实来源时叠加）与限幅 ±1.0。测试期望同步：逐步用例改为 0.02 步长（rhoNew 1.47）；E2E 收敛判据恢复为「不越零 + ≤6 步」。</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>pytest 102 全绿；verify_heavy_ash_source.js **14 项全 PASS**，关键输出：实测增益 **15%/单位密度**（与现场一致，步长偏大 1.00 倍）；逐步闭环 **2 步收敛**（偏差 0.499% → 0.199% → 0.004%，不越零）；棘轮已停；仿真门控（默认密度不再有幻象）；限幅 ±1.0；占位值守卫</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>M-15</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>按现场访谈答案改专家表口径（2026-09-12）</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>访谈三问的答案：① 偏差 0.15%→0.01、0.30%→0.02、**最多 0.03**；② 口径 = **总精煤灰分**；③ 密度最小可设 **0.005 甚至更小**。结论：现场做法 = **比例律（≈1/15 g/cm³ 每 1% 灰分）+ 封顶 0.03**，既不是纯增益律（大偏差不按比例）、也不是纯步长限幅（小偏差确实按比例）。</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>改动：专家表由「0.15→0.01、0.25→0.02、斜率 0.1 无上限」改为 **Δρ = min(|ΔA|/15, 0.03)**（死区 0.05 不变），前后端同步。旧表的问题：1.5% 偏差时给 0.145 = 现场上限的 4.8 倍；0.30% 时给 0.025 而现场是 0.02；斜率 0.1 与现场的 0.067 不符。口径确认（Q2）说明现有 deltaA 实现正确、无需改换算；Q3 说明执行器分辨率足够细，死区 0.05 与增益 15%/单位相容（半步响应 0.0375 &lt; 0.05），不必为抗极限环放宽死区。仍待定一项：建议的**单次步长上限**取 0.01/0.02/0.03（现为界面「钳制」=0.01，最保守）。</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>pytest 102 全绿（含 2 条改写后的专家表用例：0.25→1/15、1.5→封顶 0.03）；简报 golden 已按前端重新生成并通过前后端逐值对拍（证明两侧新口径一致）；verify_heavy_ash_source.js 14 项断言全 PASS（逐步 3 步收敛、棘轮已停、仿真门控/限幅、占位值守卫）；docs/密度增益标定-现场访谈提纲.xlsx 已填入答案并新增「访谈结论（2026-09-12）」Sheet</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>M-13</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>重介精煤灰分加「手动/计算」来源选择（2026-09-12 需求）</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>现场需求：密度计应能影响重介精煤灰分，但此前只要手动填过重介灰分，它就**永久压住**计算值 —— 全项目没有任何地方给重介灰分打「自动层时间点」（_autoBump('heavyAsh') 不存在），而其它仪表（皮带秤/灰分仪/液位）都有该机制。于是「把密度计调到建议值 → 重介灰分变化 → 总灰分达标」这条链走不通。</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>实现在在线仪表的重介精煤灰分行加下拉（与总精煤灰分同款）：手动=用填写的化验值；计算=502在线值 + 密度仿真（密度计因此在起作用）。默认按「升级前有手动值就是手动优先」迁移，不悄悄改变现场行为；双击填值自动切到手动（避免「填了却不生效」）；「总灰分修改」开启时该下拉随公式因素一并冻结；手动档下并列显示「计算 X.XX」供对照；决策日志 ctx 增记 heavyAshSource，导出表加「重介灰分来源」列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>M-14</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>M-14</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>闭环口径：三模型会诊结论 + 我的实测复现（原方案②已否决）</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>三路独立会诊（glm-5.3 / qwen3.8-max / qwen3.8-flash）+ 我自己复现，一致否决「把 simK 调到与专家表一致」：那只是让两个**都未标定**的常数互相对齐（循环标定），会把「真增益若为 28.9 则闭环必发散」这个最需要管理的风险从仿真里藏掉。会诊还指出：28.91% 不是测量值，而是恒等式 0.867/simK（0.867 又来自三个硬编码常量）。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>**实测复现（headless 真实浏览器 + 临时库）**：① 专家表三段**完全共线** Δρ = 0.1×(|ΔA|−0.05)，真实自由度只有 2（死区 0.05、斜率 0.1）→ 隐含增益按斜率是 10%/单位（不是割线 15%），与仿真 28.91 相差 2.89 倍；② **手动档棘轮（确认）**：同一份化验下偏差恒定 → 建议恒为 −0.043 → 密度 1.52→1.477→1.434→1.391→1.35（下限），而重介/总灰分全程不变；③ **计算档闭环震荡（确认）**：1.52→1.433→1.588→1.35→1.60→1.35…，与理论乘子 |1−0.1×28.91| = 1.891 &gt; 1（稳定条件 g&lt;20）完全吻合；④ 界面「钳制 0.01」**不作用于建议值**：偏差 1.262% → 建议 Δρ=−0.121（12 个步长）；⑤ 前后端不一致：resolvers.py 的 resolve_instrument('ash_502') 没有密度仿真项，前端有。</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>**推荐路径（五段，均带验收门槛与回退）**：P0 零成本安全守卫（不需任何标定，建议立刻做）：真钳制 maxStep；一条化验只允许一次动作（latch/驻留时间）；达标判定改为多点均值（单点化验 σ≈0.24~0.28%，远大于死区 0.05%）；重介灰分手动值等于目标值的占位值不参与建议；摘掉前端独有的仿真项或补进后端保持一致；P1 1 小时访谈判别「增益律 vs 步长限幅」，并问清 0.15 的口径（总灰分还是重介灰分）、执行机构最小可分辨步长（0.005 还是 0.01）；P2 噪声与漂移标定（保持试验、同位复验、把工作面/停机/脱粉/带煤量导到带密度的行上）；P3 受控阶跃标定真实增益 g（±0.02~0.03、ABAB、每平台≥3~4 个化验样、平行样；功效：0.01 步长需 n≈267，0.03 只需约 30 —— 约 3~5 个生产日）；P4 影子运行后按「专家表先验 + 数据后验」收缩合并上线（Δρ = λ(|ΔA|−死区)/Ĝ，λ≈0.5，死区随 Ĝ 与执行分辨率自适应），任一指标恶化自动回退并记录原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>M-12</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>第二次数据损失 + 根因修复：快照只拥有它携带的表（2026-09-11/12）</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>为验证 M-10 的 force 前置备份，我把 `GET /api/v1/state` 的结果**原样 force 写回**，以为「内容相同所以无害」。但 GET /state 只返回 24 个键，**不含** manualEntries / importLogs / alerts / coarseModelHistory / heavySamples，而 force 当时是整库删空再按载荷重写 → 这几张表被静默清空（manual_entries 242 → 0、import_logs 3 → 0、alerts 1 → 0、coarse_model_history 1 → 0）。与 16:25 那次事故同根：**缺键 ≠ 空表**。</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>恢复：停止服务 → 现场快照留证 → 用 **16:33:03 那次 force 之前自动生成的备份**（M-10 的机制，正好是损失前的完整状态：242/3/1 + coarse_model_history 1 + ash_target 8.55）覆盖回库 → 删 WAL → 重启核对，逐表一致。根因修复：migrate.replace 的写入范围改由「载荷里实际出现哪些键」决定（TABLE_OWNER_KEYS）：缺键的表一律不碰；settings/auto_state 不再整表删除、只按携带的键 upsert；响应新增 owned / untouched 两个字段，把「这次到底动了哪些表」显式报出来。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>M-11</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>新增「实测密度计」（仅展示，2026-09-11 需求）</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>现场已知在线密度计存在测量误差，希望把人工实测密度作为更权威的参考。但密度指导是**按总灰分线性指导**的：它只对「调整量(Δρ)」敏感，对密度计读数本身不敏感 —— 所以换哪台密度计对系统行为都没有影响。因此本次**只做展示**，不接进任何计算。</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>两个展示位置：① 采集页「在线仪表实时数据」表新增一行「实测密度计」；② 总览页「合并系统」卡片新增「实测密度」一项并显示与在线密度计的偏差 Δ（|Δ|&gt;0.02 标黄）。取值层级与其它仪表同构：双击手动 &gt; 补录录入（calcLogs/density_actual）&gt; **无默认**（未录入显示 —，刻意不给仪表默认值，避免用在线值冒充实测值）；输入 1.30~1.65 之外拒收，1.35~1.60 之外仅质量状态标黄；决策日志 ctx 增记 densityActual（仅记录，便于以后标定两台密度计误差），导出表加「实测密度」列。</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>新增 backend/scripts/verify_density_actual.js（13 项断言，已进 CI）：行存在/初始未录入、手动录入、Δ 计算、硬限拒收、软限标黄、补录回落录入层、卡片显示与 Δ、ctx 记录、导出列；**其中 CALC_UNAFFECTED 是关键不变量**：设置实测密度前后，建议密度/总灰分/重介灰分/粗精灰分/浮精灰分/总煤量逐项一致 —— 以后若有人把实测密度接进计算，这条会立刻变红。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>M-8</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>M-9</t>
+          <t>M-8</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
+          <t>写接口访问控制：token + force 只许本机（2026-09-11）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
+          <t>服务 bind 0.0.0.0，此前**零鉴权**：同网段任意主机一条 curl 就能整库覆盖或清空（529 条测量记录、242 条补录、密度决策日志、模型参数）。现所有写接口要求 X-DMCS-Token（token 首次启动自动生成并持久化到 backend/data/write_token.txt，随首页以 &lt;meta&gt; 下发 → 浏览器零配置）；本机回环免 token（现场脚本/E2E 从本机发起）；**PUT /state?force=true 只接受本机来源**（拿到 token 也不能从别的机器洗库）。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
+          <t>10 条 pytest（远端无 token 401、带 token 通过、错 token 401、回环免 token、六个写接口逐条点名、force 远端 403 而本机放行、首页注入/关闭时不注入、token 落盘复用）；**真实网络实测**（局域网地址 192.168.43.104）：无 token → 401、带 token → 200、force → 403、回环 force → 200、读接口 → 200、首页含本次 token；**真实浏览器实测**：从局域网地址打开页面跑完整 E2E（镜像 12 项断言 + 决策日志）全 PASS —— 证明「页面下发 token → api.js 自动带上 → 写接口放行」这条链可用。挡不住的（已在 auth.py 写明）：能打开页面的人能读到 token；能登录服务器本机的人。pytest 80 → 93</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-9</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+          <t>事故与恢复：我用一条 force PUT 清空了真实库（2026-09-11）</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+          <t>在验证 M-8 的鉴权时，我的核对脚本为了测试「回环 force 放行」，向**真实库**发送了一个**空 store + force=true** 的请求 —— force 按设计绕过防回退守卫，于是 11 张业务表全部被清空（coal_records 529 → 0，manual_entries 242 → 0，settings/auto_state 亦为 0）。这是我在本 session 里造成的唯一一次数据事故，根因是**验证脚本对着生产库执行破坏性操作**。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+          <t>恢复：立即停服务（防 checkpoint 截断 WAL）→ 快照 db/-wal/-shm 两份 → 解析 WAL 帧与提交边界，发现主库文件停在 15:37 的 checkpoint、而删除发生在 16:25，**删除前的页镜像完整保留在主库文件里**（WAL 中只有删除后的写入）→ 丢弃 WAL → 数据全部回来：coal_records 529（coarse 152 / float 17 / ash_density 360）、manual_entries 242、import_logs 3、alerts 1、coarse_models 2、coarse_model_history 1、settings 8、auto_state 11，与事故前逐项一致；仅 ash_target 回到 15:37 的 8.61，已改回真实的 8.55。注意：能恢复**靠的是运气**（主库恰好没被 checkpoint），不是机制。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>M-9 的系统性防护：force 覆盖前自动备份 + 工具纪律</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>① migrate.replace(force=True) 在清库**之前**用 sqlite3 在线备份 API（Connection.backup，含 WAL 中最新事务）在库文件旁生成带毫秒时间戳的快照，路径写在响应的 backup 字段，保留最近 20 份；非 force 的普通镜像不备份（否则每次镜像都复制整个库）。② 备份文件名带毫秒并防碰撞 —— 第一版用秒级时间戳，同一秒内「覆盖→回滚」的两次 force 会撞名互相覆盖，把回滚点弄丢（被 test_backup 的回滚演练断言抓到）。③ 工具纪律：破坏性操作只对临时库执行；补丁脚本的每一次替换都要断言命中（本次另有一处 api.js 的 header 注入因锚点不符而**静默未生效**，是 E2E 断言把它抓出来的）。</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>新增 3 条 pytest（force 返回的备份里必须是覆盖前的三类记录、普通写入不备份、备份数量有上限）；**生产库实测**：原样 force 写回一次 → 响应给出备份路径，备份文件 385 KB 存在，写回后 152/17/360 与 ashTarget 8.55 均未变；pytest 93 全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>M-7</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>方案D：整库镜像对「浏览器收不到的表」改为只增不删</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>原先整库 PUT 会 wipe 并按 payload 重写 manual_entries / import_logs / alerts / regression_models / coarse_model_history，而 GET /state **不返回**它们、后端也只由镜像写入—— 两端不可能收敛：纳入守卫会让「列表较短」的浏览器永久拒写（M-1 病理），照删照写又会在多浏览器/清库场景下静默删掉服务器上的行。改为按自然键合并、只增不删（force=true 仍整体覆盖）。</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>新增 3 条 pytest（短列表镜像不删历史、新行能上行且不重复插、告警条件消失不清库），pytest 78 → 80 全绿；**真实库实证**：发送 manualEntries/alerts/importLogs 全空的镜像后，manual_entries 242 / import_logs 3 / alerts 1 / coarse_models 2 / coarse_model_history 1 全部不变，响应带 merged 计数；E2E 与决策日志脚本在新后端上复跑仍全 PASS。后续项：「清空补录历史」的界面文案应说明只清本地，或加一个显式的 force 清服务器入口。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>M-6</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>E2E 自身的空转假 PASS（方法论教训，已修）</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>第一版用例1 把探针值设成 8.61，而服务器遗留值恰好也是 8.61 → 新快照与「上次已发送内容」逐字节相同，被「内容相同则跳过」短路，**什么都没发**；后续断言又恰好对上遗留值，于是 4 条断言全绿却是空转。现在：探针值必须同时不同于服务器值与浏览器值，并额外断言 stub 被调用次数 === 1（防空转），失败时打印 debug 快照。</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>诊断脚本逐步打印 _mirrorPending/_mirrorSent/待发键/stats，确认机制本身正常（calls:1 / failures:1 / saved:yes / 提示出现）后才定位到是用例自己的问题</t>
         </is>

--- a/docs/待办-后续优化计划.xlsx
+++ b/docs/待办-后续优化计划.xlsx
@@ -18,6 +18,7 @@
     <sheet name="写路径评审与修复" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="写接口鉴权与事故复盘" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="实测密度计(仅展示)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="密度建议守卫缺陷复盘" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1137,6 +1138,278 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>现场实测反馈：改了化验，建议密度却不动 —— 最短驻留把新化验一起挡掉了</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>议题</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>现象 / 结论</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>原因（为什么会这样）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>修法与守卫</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>现场反馈（原话）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>「密度计 1.532、重介精煤灰分 7.8346、总灰分 8.4975 → 灰分达标、建议 1.532，没问题；但把重介精煤灰分调到 8.3、总灰分 8.9（不达标），为什么建议密度还是 1.532？」</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>操作员的预期是：**我录了新化验，你就该按新化验重新算**。建议值不动，在现场看来就是系统坏了 —— 而它其实是被 P0 安全守卫挡住了，且界面上看不出来。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>本表记录这个缺陷的现象、根因、修法与守卫；同类缺陷（守卫挡住真实新数据）以后照此表排查：先看 guard 的三个状态位谁先命中，再看数据时间戳与动作时刻的先后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>复现（机器）</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>verify_dwell_bypass.js：标定出使总灰分=目标的达标点 → 密度 1.532 → 写回同值 → 录入新化验（重介灰分 +0.4654）→ 修复前 hold=true、建议 1.532；修复后 hold=false、建议 1.512。</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>修复前该脚本 11 项断言里 9 项 FAIL；修复后 11 项全 PASS。</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>已进 CI（用例5，allowReal=1）：现场若再出现「建议不动」，CI 会先在机器上抓住它。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>根因①：驻留不看有没有新化验</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>densityGuardState 的驻留分支只判断「距上次改密度不足 30 分钟」就 hold，完全不看这段时间里有没有新化验进来。</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>驻留（P0③）的本意是**等过程到位 + 等新化验**这两件事；逻辑上「新化验到了」正是它等待的终点，却被写成了「时间没到就一直挡」——把等待条件当成了禁止条件。结果：录了新化验、偏差明明不达标，建议仍停在旧值。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>新增 _densityManualEpoch()（最近一次人工录入且当前在用的灰分化验时刻）：它晚于 densityLastMoveAt → dataIsNewer → **不放 hold**，并在建议理由里写明「距上次调密 X 分钟，此后已录入新的化验值」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>根因②：同值写入也算动过密度</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>把建议值原样写回（自动执行到位后重复写、操作员手填与当前相同的值）也会走 setInstrumentInput 的密度分支 → 记 densityLastMoveAt + 闩锁 → 凭空起一个 30 分钟驻留窗口。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>「动作」被定义成了「调用写接口」，而不是「密度真的变了」。大量无害的同值写入于是各自清空了一次建议窗口，把后续真实建议一起挡在门外。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>写入前先比当前值：|新值−当前值| ≤ 1e-9 视为**没动作** → 不记变动时刻、不记闩锁（建议仍然有效，不会被误当成已执行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>根因③（界面）：hold 借用「达标保持」</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>卡片副标题在 hold 时也写「达标保持」，与真正达标时长得一模一样。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>界面文案只看了 direction，没看 hold；而 hold 分支恰好把 direction 设成 stable。两者叠加，现场的读法就是「系统说已达标」。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>hold 时副标题写「保持（等新化验/新数据）」；总览卡片详情弹窗的「达标判定」行也改为显示 hold 及其原因，不再冒充达标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>修法④：闩锁对象改为当前数据</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>_latchDensityAction() 原先记「上次给出建议时的那份数据」，中间若发生过达标/切方案就会记错对象。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>操作员是对着**眼前这份数据**动的密度，闩锁要盖住的也应该是这份数据。</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>改为在动作时刻现算当前驱动键（数据不全时回退旧键）；E2E 断言 REAL_MOVE_ARMS_LATCH / LATCH_STILL_ONE_ACTION_PER_SAMPLE 守住该语义。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>为什么在线/导入数据不算「新化验」</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>「新化验」的口径 = 人工录入且当前真正在用的灰分（总灰分/重介/浮精/粗精煤泥手动值）。三表记录、导入的在线数据连续刷新**不**放行驻留。</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>在线数据是连续流：若每次刷新都放行驻留，自动执行会追着在线噪声一路动密度 —— 那正是 P0③ 要防的。而化验是离散的、人给的一次判断，放行它符合现场节奏。顺带：import.js 会 _onExternalInput() 让自动执行重算目标，所以这条边界必须画清楚。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>界线写在 _densityManualEpoch() 的注释里；将来若要把在线数据也纳入放行条件，必须先解决「连续流不得直接驱动步进」这个问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>为什么不干脆去掉驻留</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>保留 P0③：没有新数据时驻留照旧生效，E2E 用 DWELL_HOLDS_WITHOUT_NEW_DATA 显式断言。</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>密度变动后产品要经过分选、脱水、取样、化验才反映出来；在这之前反复动密度只会把回路推成振荡。用户反馈的是「被挡得看不见原因」，不是「不该挡」。</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>因此修的是「判定条件」与「可见性」，不是把守卫拆掉。若 P3 阶跃实验测出过程时间常数，30 分钟窗口应改为按实测滞后设定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>放行时的取样时刻提示</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>放行意见里附提示：「这份化验距调密时间很近，若它是调密前取的煤样，请以下一份化验为准」（&lt;5 分钟时追加）。</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>系统只知道**录数时刻**，不知道**取样时刻**；调密后 2 分钟送来的化验，测的多半还是旧密度下的产品。把这条不确定性说给操作员，比替他猜更安全。</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>遗留：若现场化验单带取样时间，把它一起录进来（heavyAshInput.sampleAt），放行条件就能从「录数晚于调密」升级为「取样晚于调密」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>影响面</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>只改前端 app.js / overview.js；后端 compute_density_guidance 的 hold 与 hold_reason 一直由前端传入，口径未变，无需改动。</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>守卫状态是**前端算、后端用**的设计（state 传入 hold/hold_reason），所以这类修改天然不会造成前后端口径分叉。</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>pytest 104 全绿；五个 E2E 脚本（镜像写路径/决策日志/实测密度计/重介灰分闭环/驻留放行）在同一个临时库上顺序执行全部 PASS。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
